--- a/Master_tarif.xlsx
+++ b/Master_tarif.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hasil Minggu Ini\Essa-Store-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{25F2563A-F76A-4D18-92AA-AD406D4C1C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F797685-57D3-45D2-B1A9-2D1B250A8F88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{CECA2AD4-CD37-44C0-91AC-A97D1185B198}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{CECA2AD4-CD37-44C0-91AC-A97D1185B198}"/>
   </bookViews>
   <sheets>
     <sheet name="SKU_Pengsup" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="796">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="804">
   <si>
     <t>Nomor SKU</t>
   </si>
@@ -2431,6 +2431,30 @@
   </si>
   <si>
     <t>HMD-L</t>
+  </si>
+  <si>
+    <t>Jenis</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>PACK</t>
+  </si>
+  <si>
+    <t>HANGTAG</t>
+  </si>
+  <si>
+    <t>WOVEN</t>
+  </si>
+  <si>
+    <t>HTROPE</t>
+  </si>
+  <si>
+    <t>THREAD</t>
+  </si>
+  <si>
+    <t>AKRILIK</t>
   </si>
 </sst>
 </file>
@@ -2440,7 +2464,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;Rp&quot;#,##0"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2481,6 +2505,13 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -2564,7 +2595,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2590,6 +2621,8 @@
     <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="40% - Accent3" xfId="2" builtinId="39"/>
@@ -2926,7 +2959,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FD8F914-C444-47BA-9F60-B10F23023A52}">
-  <dimension ref="A1:C770"/>
+  <dimension ref="A1:F770"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" bestFit="1" customWidth="1"/>
@@ -2935,7 +2968,7 @@
     <col min="4" max="4" width="21.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2945,15 +2978,27 @@
       <c r="C1" s="6" t="s">
         <v>598</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E1" s="11" t="s">
+        <v>796</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="2"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E2" s="12" t="s">
+        <v>799</v>
+      </c>
+      <c r="F2" s="12">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
@@ -2963,8 +3008,14 @@
       <c r="C3" s="2">
         <v>2000</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E3" s="12" t="s">
+        <v>800</v>
+      </c>
+      <c r="F3" s="12">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
@@ -2974,8 +3025,14 @@
       <c r="C4" s="2">
         <v>2200</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E4" s="12" t="s">
+        <v>801</v>
+      </c>
+      <c r="F4" s="12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
@@ -2986,7 +3043,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
@@ -2997,7 +3054,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
@@ -3008,7 +3065,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>7</v>
       </c>
@@ -3019,7 +3076,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>8</v>
       </c>
@@ -3030,7 +3087,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>9</v>
       </c>
@@ -3041,7 +3098,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>10</v>
       </c>
@@ -3052,7 +3109,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>11</v>
       </c>
@@ -3063,7 +3120,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>12</v>
       </c>
@@ -3074,7 +3131,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>13</v>
       </c>
@@ -3085,7 +3142,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>14</v>
       </c>
@@ -3096,7 +3153,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>15</v>
       </c>
@@ -9601,97 +9658,139 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96A5A135-A07A-4862-A4A7-EC4AA886D053}">
-  <dimension ref="A1:B659"/>
+  <dimension ref="A1:F659"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" customWidth="1"/>
     <col min="2" max="2" width="31.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>772</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>773</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E1" s="11" t="s">
+        <v>796</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>774</v>
       </c>
       <c r="B2" s="8">
         <v>900</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E2" t="s">
+        <v>798</v>
+      </c>
+      <c r="F2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>775</v>
       </c>
       <c r="B3" s="8">
         <v>1000</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E3" t="s">
+        <v>799</v>
+      </c>
+      <c r="F3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>776</v>
       </c>
       <c r="B4">
         <v>700</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E4" t="s">
+        <v>800</v>
+      </c>
+      <c r="F4">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>777</v>
       </c>
       <c r="B5">
         <v>1000</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E5" t="s">
+        <v>801</v>
+      </c>
+      <c r="F5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>778</v>
       </c>
       <c r="B6">
         <v>600</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>802</v>
+      </c>
+      <c r="F6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>803</v>
+      </c>
+      <c r="F7">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>780</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>781</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>782</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>783</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>784</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>785</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>786</v>
       </c>
@@ -9699,12 +9798,12 @@
         <v>700</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>787</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>788</v>
       </c>

--- a/Master_tarif.xlsx
+++ b/Master_tarif.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hasil Minggu Ini\Essa-Store-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E1A1BC-6027-41B4-A3C0-79EF6F0DC802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEB98363-5944-4CF5-A313-B4C20D58BCFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{CECA2AD4-CD37-44C0-91AC-A97D1185B198}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{CECA2AD4-CD37-44C0-91AC-A97D1185B198}"/>
   </bookViews>
   <sheets>
     <sheet name="SKU_Pengsup" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="656">
   <si>
     <t>Nomor SKU</t>
   </si>
@@ -1939,6 +1939,78 @@
   </si>
   <si>
     <t>SA-Fossil-XL</t>
+  </si>
+  <si>
+    <t>PVR-INS-Noir</t>
+  </si>
+  <si>
+    <t>PVR-INS-Mahogany</t>
+  </si>
+  <si>
+    <t>PVR-INS-Ivory</t>
+  </si>
+  <si>
+    <t>PVR-INS-Navy</t>
+  </si>
+  <si>
+    <t>PVR-INS-Pink Blush</t>
+  </si>
+  <si>
+    <t>PVR-INS-Burgundy</t>
+  </si>
+  <si>
+    <t>PVR-INS-Cocoa</t>
+  </si>
+  <si>
+    <t>PVR-INS-Silver Mist</t>
+  </si>
+  <si>
+    <t>PVR-INS-Charcoal</t>
+  </si>
+  <si>
+    <t>PVR-INS-Mocha</t>
+  </si>
+  <si>
+    <t>PVR-INS-Taupe</t>
+  </si>
+  <si>
+    <t>PVR-INS-Sand</t>
+  </si>
+  <si>
+    <t>PVR-SWL-Noir</t>
+  </si>
+  <si>
+    <t>PVR-SWL-Mahogany</t>
+  </si>
+  <si>
+    <t>PVR-SWL-Ivory</t>
+  </si>
+  <si>
+    <t>PVR-SWL-Navy</t>
+  </si>
+  <si>
+    <t>PVR-SWL-Pink Blush</t>
+  </si>
+  <si>
+    <t>PVR-SWL-Burgundy</t>
+  </si>
+  <si>
+    <t>PVR-SWL-Cocoa</t>
+  </si>
+  <si>
+    <t>PVR-SWL-Silver Mist</t>
+  </si>
+  <si>
+    <t>PVR-SWL-Charcoal</t>
+  </si>
+  <si>
+    <t>PVR-SWL-Mocha</t>
+  </si>
+  <si>
+    <t>PVR-SWL-Taupe</t>
+  </si>
+  <si>
+    <t>PVR-SWL-Sand</t>
   </si>
 </sst>
 </file>
@@ -8704,123 +8776,231 @@
       <c r="I598"/>
     </row>
     <row r="599" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A599" s="7"/>
-      <c r="C599" s="2"/>
+      <c r="A599" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="C599" s="2">
+        <v>3500</v>
+      </c>
       <c r="I599"/>
     </row>
     <row r="600" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A600" s="7"/>
-      <c r="C600" s="2"/>
+      <c r="A600" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="C600" s="2">
+        <v>3500</v>
+      </c>
       <c r="I600"/>
     </row>
     <row r="601" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A601" s="7"/>
-      <c r="C601" s="2"/>
+      <c r="A601" s="5" t="s">
+        <v>634</v>
+      </c>
+      <c r="C601" s="2">
+        <v>3500</v>
+      </c>
       <c r="I601"/>
     </row>
     <row r="602" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A602" s="7"/>
-      <c r="C602" s="2"/>
+      <c r="A602" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="C602" s="2">
+        <v>3500</v>
+      </c>
       <c r="I602"/>
     </row>
     <row r="603" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A603" s="7"/>
-      <c r="C603" s="2"/>
+      <c r="A603" s="5" t="s">
+        <v>636</v>
+      </c>
+      <c r="C603" s="2">
+        <v>3500</v>
+      </c>
       <c r="I603"/>
     </row>
     <row r="604" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A604" s="7"/>
-      <c r="C604" s="2"/>
+      <c r="A604" s="5" t="s">
+        <v>637</v>
+      </c>
+      <c r="C604" s="2">
+        <v>3500</v>
+      </c>
       <c r="I604"/>
     </row>
     <row r="605" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A605" s="7"/>
-      <c r="C605" s="2"/>
+      <c r="A605" s="5" t="s">
+        <v>638</v>
+      </c>
+      <c r="C605" s="2">
+        <v>3500</v>
+      </c>
       <c r="I605"/>
     </row>
     <row r="606" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A606" s="7"/>
-      <c r="C606" s="2"/>
+      <c r="A606" s="5" t="s">
+        <v>639</v>
+      </c>
+      <c r="C606" s="2">
+        <v>3500</v>
+      </c>
       <c r="I606"/>
     </row>
     <row r="607" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A607" s="7"/>
-      <c r="C607" s="2"/>
+      <c r="A607" s="5" t="s">
+        <v>640</v>
+      </c>
+      <c r="C607" s="2">
+        <v>3500</v>
+      </c>
       <c r="I607"/>
     </row>
     <row r="608" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A608" s="7"/>
-      <c r="C608" s="2"/>
+      <c r="A608" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="C608" s="2">
+        <v>3500</v>
+      </c>
       <c r="I608"/>
     </row>
     <row r="609" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A609" s="7"/>
-      <c r="C609" s="2"/>
+      <c r="A609" s="5" t="s">
+        <v>642</v>
+      </c>
+      <c r="C609" s="2">
+        <v>3500</v>
+      </c>
       <c r="I609"/>
     </row>
     <row r="610" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A610" s="7"/>
-      <c r="C610" s="2"/>
+      <c r="A610" s="5" t="s">
+        <v>643</v>
+      </c>
+      <c r="C610" s="2">
+        <v>3500</v>
+      </c>
       <c r="I610"/>
     </row>
     <row r="611" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A611" s="7"/>
-      <c r="C611" s="2"/>
+      <c r="A611" s="5" t="s">
+        <v>644</v>
+      </c>
+      <c r="B611" s="4"/>
+      <c r="C611" s="2">
+        <v>2200</v>
+      </c>
       <c r="I611"/>
     </row>
     <row r="612" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A612" s="7"/>
-      <c r="C612" s="2"/>
+      <c r="A612" s="5" t="s">
+        <v>645</v>
+      </c>
+      <c r="B612" s="4"/>
+      <c r="C612" s="2">
+        <v>2200</v>
+      </c>
       <c r="I612"/>
     </row>
     <row r="613" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A613" s="7"/>
-      <c r="C613" s="2"/>
+      <c r="A613" s="5" t="s">
+        <v>646</v>
+      </c>
+      <c r="B613" s="4"/>
+      <c r="C613" s="2">
+        <v>2200</v>
+      </c>
       <c r="I613"/>
     </row>
     <row r="614" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A614" s="7"/>
-      <c r="C614" s="2"/>
+      <c r="A614" s="5" t="s">
+        <v>647</v>
+      </c>
+      <c r="B614" s="4"/>
+      <c r="C614" s="2">
+        <v>2200</v>
+      </c>
       <c r="I614"/>
     </row>
     <row r="615" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A615" s="7"/>
-      <c r="C615" s="2"/>
+      <c r="A615" s="5" t="s">
+        <v>648</v>
+      </c>
+      <c r="B615" s="4"/>
+      <c r="C615" s="2">
+        <v>2200</v>
+      </c>
       <c r="I615"/>
     </row>
     <row r="616" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A616" s="7"/>
-      <c r="C616" s="2"/>
+      <c r="A616" s="5" t="s">
+        <v>649</v>
+      </c>
+      <c r="B616" s="4"/>
+      <c r="C616" s="2">
+        <v>2200</v>
+      </c>
       <c r="I616"/>
     </row>
     <row r="617" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A617" s="7"/>
-      <c r="C617" s="2"/>
+      <c r="A617" s="5" t="s">
+        <v>650</v>
+      </c>
+      <c r="B617" s="4"/>
+      <c r="C617" s="2">
+        <v>2200</v>
+      </c>
       <c r="I617"/>
     </row>
     <row r="618" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A618" s="7"/>
-      <c r="C618" s="2"/>
+      <c r="A618" s="5" t="s">
+        <v>651</v>
+      </c>
+      <c r="B618" s="4"/>
+      <c r="C618" s="2">
+        <v>2200</v>
+      </c>
       <c r="I618"/>
     </row>
     <row r="619" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A619" s="7"/>
-      <c r="C619" s="2"/>
+      <c r="A619" s="5" t="s">
+        <v>652</v>
+      </c>
+      <c r="B619" s="4"/>
+      <c r="C619" s="2">
+        <v>2200</v>
+      </c>
       <c r="I619"/>
     </row>
     <row r="620" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A620" s="7"/>
-      <c r="C620" s="2"/>
+      <c r="A620" s="5" t="s">
+        <v>653</v>
+      </c>
+      <c r="B620" s="4"/>
+      <c r="C620" s="2">
+        <v>2200</v>
+      </c>
       <c r="I620"/>
     </row>
     <row r="621" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A621" s="7"/>
-      <c r="C621" s="2"/>
+      <c r="A621" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="B621" s="4"/>
+      <c r="C621" s="2">
+        <v>2200</v>
+      </c>
       <c r="I621"/>
     </row>
     <row r="622" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A622" s="7"/>
-      <c r="C622" s="2"/>
+      <c r="A622" s="5" t="s">
+        <v>655</v>
+      </c>
+      <c r="B622" s="4"/>
+      <c r="C622" s="2">
+        <v>2200</v>
+      </c>
       <c r="I622"/>
     </row>
     <row r="623" spans="1:9" x14ac:dyDescent="0.25">

--- a/Master_tarif.xlsx
+++ b/Master_tarif.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hasil Minggu Ini\Essa-Store-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEB98363-5944-4CF5-A313-B4C20D58BCFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{231FB12D-9B8C-4B02-9740-BECDE5574EF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{CECA2AD4-CD37-44C0-91AC-A97D1185B198}"/>
+    <workbookView xWindow="2430" yWindow="3045" windowWidth="28800" windowHeight="15345" xr2:uid="{CECA2AD4-CD37-44C0-91AC-A97D1185B198}"/>
   </bookViews>
   <sheets>
     <sheet name="SKU_Pengsup" sheetId="1" r:id="rId1"/>
     <sheet name="SKU_Penjahit" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">SKU_Pengsup!$A$1:$B$626</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">SKU_Pengsup!$A$1:$B$662</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="705">
   <si>
     <t>Nomor SKU</t>
   </si>
@@ -2011,6 +2011,153 @@
   </si>
   <si>
     <t>PVR-SWL-Sand</t>
+  </si>
+  <si>
+    <t>JSO-Almond (akrilik)</t>
+  </si>
+  <si>
+    <t>JSO-Army (akrilik)</t>
+  </si>
+  <si>
+    <t>JSO-Babypink (akrilik)</t>
+  </si>
+  <si>
+    <t>JSO-Bata (akrilik)</t>
+  </si>
+  <si>
+    <t>JSO-Beige (akrilik)</t>
+  </si>
+  <si>
+    <t>JSO-Burgundy (akrilik)</t>
+  </si>
+  <si>
+    <t>JSO-Caramel (akrilik)</t>
+  </si>
+  <si>
+    <t>JSO-Choco (akrilik)</t>
+  </si>
+  <si>
+    <t>JSO-Cokelat Tua (akrilik)</t>
+  </si>
+  <si>
+    <t>JSO-Coksu (akrilik)</t>
+  </si>
+  <si>
+    <t>JSO-Cream (akrilik)</t>
+  </si>
+  <si>
+    <t>JSO-Dark Grey (akrilik)</t>
+  </si>
+  <si>
+    <t>JSO-Denim (akrilik)</t>
+  </si>
+  <si>
+    <t>JSO-Dusty Pink (akrilik)</t>
+  </si>
+  <si>
+    <t>JSO-Fossil (akrilik)</t>
+  </si>
+  <si>
+    <t>JSO-Grey (akrilik)</t>
+  </si>
+  <si>
+    <t>JSO-Hazelnut (akrilik)</t>
+  </si>
+  <si>
+    <t>JSO-Hitam (akrilik)</t>
+  </si>
+  <si>
+    <t>JSO-Jotol (akrilik)</t>
+  </si>
+  <si>
+    <t>JSO-Lilac (akrilik)</t>
+  </si>
+  <si>
+    <t>JSO-Lime (akrilik)</t>
+  </si>
+  <si>
+    <t>JSO-Maroon (akrilik)</t>
+  </si>
+  <si>
+    <t>JSO-Mint (akrilik)</t>
+  </si>
+  <si>
+    <t>JSO-Misty (akrilik)</t>
+  </si>
+  <si>
+    <t>JSO-Moca (akrilik)</t>
+  </si>
+  <si>
+    <t>JSO-Mustard (akrilik)</t>
+  </si>
+  <si>
+    <t>JSO-Navy (akrilik)</t>
+  </si>
+  <si>
+    <t>JSO-Olive (akrilik)</t>
+  </si>
+  <si>
+    <t>JSO-Putih (akrilik)</t>
+  </si>
+  <si>
+    <t>JSO-Putih Tulang (akrilik)</t>
+  </si>
+  <si>
+    <t>JSO-Sage (akrilik)</t>
+  </si>
+  <si>
+    <t>JSO-Smoke (akrilik)</t>
+  </si>
+  <si>
+    <t>JSO-Softpink (akrilik)</t>
+  </si>
+  <si>
+    <t>JSO-Taro (akrilik)</t>
+  </si>
+  <si>
+    <t>JSO-Tosca (akrilik)</t>
+  </si>
+  <si>
+    <t>JSO-Turkish (akrilik)</t>
+  </si>
+  <si>
+    <t>Obres</t>
+  </si>
+  <si>
+    <t>BVR-TBN-Noir</t>
+  </si>
+  <si>
+    <t>BVR-TBN-Mahogany</t>
+  </si>
+  <si>
+    <t>BVR-TBN-Ivory</t>
+  </si>
+  <si>
+    <t>BVR-TBN-Navy</t>
+  </si>
+  <si>
+    <t>BVR-TBN-Pink Blush</t>
+  </si>
+  <si>
+    <t>BVR-TBN-Burgundy</t>
+  </si>
+  <si>
+    <t>BVR-TBN-Cocoa</t>
+  </si>
+  <si>
+    <t>BVR-TBN-Silver Mist</t>
+  </si>
+  <si>
+    <t>BVR-TBN-Charcoal</t>
+  </si>
+  <si>
+    <t>BVR-TBN-Mocha</t>
+  </si>
+  <si>
+    <t>BVR-TBN-Taupe</t>
+  </si>
+  <si>
+    <t>BVR-TBN-Sand</t>
   </si>
 </sst>
 </file>
@@ -2020,7 +2167,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;Rp&quot;#,##0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2043,11 +2190,6 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2149,9 +2291,9 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2167,18 +2309,15 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="3" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="3" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2518,7 +2657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FD8F914-C444-47BA-9F60-B10F23023A52}">
-  <dimension ref="A1:I770"/>
+  <dimension ref="A1:I806"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" bestFit="1" customWidth="1"/>
@@ -2539,30 +2678,30 @@
       <c r="C1" s="6" t="s">
         <v>450</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>612</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="10" t="s">
         <v>613</v>
       </c>
       <c r="I1"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="2"/>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="11" t="s">
         <v>615</v>
       </c>
-      <c r="F2" s="12">
+      <c r="F2" s="11">
         <v>97</v>
       </c>
       <c r="I2"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="12" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="4">
@@ -2571,16 +2710,16 @@
       <c r="C3" s="2">
         <v>2000</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="11">
         <v>150</v>
       </c>
       <c r="I3"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="4">
@@ -2589,16 +2728,16 @@
       <c r="C4" s="2">
         <v>2200</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>617</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="11">
         <v>20</v>
       </c>
       <c r="I4"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="12" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="4">
@@ -2610,7 +2749,7 @@
       <c r="I5"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="12" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="4">
@@ -2622,7 +2761,7 @@
       <c r="I6"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="12" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="4">
@@ -2634,7 +2773,7 @@
       <c r="I7"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="12" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="4">
@@ -2646,7 +2785,7 @@
       <c r="I8"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="12" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="4">
@@ -2658,7 +2797,7 @@
       <c r="I9"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="12" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="4">
@@ -2670,7 +2809,7 @@
       <c r="I10"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="12" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="4">
@@ -2682,7 +2821,7 @@
       <c r="I11"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="12" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="4">
@@ -2694,7 +2833,7 @@
       <c r="I12"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="12" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="4">
@@ -2706,7 +2845,7 @@
       <c r="I13"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="12" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="4">
@@ -2718,7 +2857,7 @@
       <c r="I14"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="12" t="s">
         <v>14</v>
       </c>
       <c r="B15" s="4">
@@ -2730,7 +2869,7 @@
       <c r="I15"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="12" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="4">
@@ -2742,7 +2881,7 @@
       <c r="I16"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="12" t="s">
         <v>16</v>
       </c>
       <c r="B17" s="4">
@@ -2754,7 +2893,7 @@
       <c r="I17"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="12" t="s">
         <v>17</v>
       </c>
       <c r="B18" s="4">
@@ -2766,7 +2905,7 @@
       <c r="I18"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="12" t="s">
         <v>18</v>
       </c>
       <c r="B19" s="4">
@@ -2778,7 +2917,7 @@
       <c r="I19"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="12" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="4">
@@ -2790,7 +2929,7 @@
       <c r="I20"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="12" t="s">
         <v>20</v>
       </c>
       <c r="B21" s="4">
@@ -2802,7 +2941,7 @@
       <c r="I21"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="12" t="s">
         <v>21</v>
       </c>
       <c r="B22" s="4">
@@ -2814,7 +2953,7 @@
       <c r="I22"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="12" t="s">
         <v>22</v>
       </c>
       <c r="B23" s="4">
@@ -2826,7 +2965,7 @@
       <c r="I23"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="12" t="s">
         <v>23</v>
       </c>
       <c r="B24" s="4">
@@ -2838,7 +2977,7 @@
       <c r="I24"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="12" t="s">
         <v>24</v>
       </c>
       <c r="B25" s="4">
@@ -2850,7 +2989,7 @@
       <c r="I25"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="12" t="s">
         <v>25</v>
       </c>
       <c r="B26" s="4">
@@ -2862,7 +3001,7 @@
       <c r="I26"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="12" t="s">
         <v>26</v>
       </c>
       <c r="B27" s="4">
@@ -2874,7 +3013,7 @@
       <c r="I27"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="12" t="s">
         <v>27</v>
       </c>
       <c r="B28" s="4">
@@ -2886,7 +3025,7 @@
       <c r="I28"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="13" t="s">
+      <c r="A29" s="12" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="4">
@@ -2898,7 +3037,7 @@
       <c r="I29"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="13" t="s">
+      <c r="A30" s="12" t="s">
         <v>445</v>
       </c>
       <c r="B30" s="4">
@@ -2910,7 +3049,7 @@
       <c r="I30"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="12" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="4">
@@ -2922,7 +3061,7 @@
       <c r="I31"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="13" t="s">
+      <c r="A32" s="12" t="s">
         <v>30</v>
       </c>
       <c r="B32" s="4">
@@ -2934,7 +3073,7 @@
       <c r="I32"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="13" t="s">
+      <c r="A33" s="12" t="s">
         <v>31</v>
       </c>
       <c r="B33" s="4">
@@ -2946,7 +3085,7 @@
       <c r="I33"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="13" t="s">
+      <c r="A34" s="12" t="s">
         <v>32</v>
       </c>
       <c r="B34" s="4">
@@ -2958,7 +3097,7 @@
       <c r="I34"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="13" t="s">
+      <c r="A35" s="12" t="s">
         <v>33</v>
       </c>
       <c r="B35" s="4">
@@ -2970,7 +3109,7 @@
       <c r="I35"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="13" t="s">
+      <c r="A36" s="12" t="s">
         <v>34</v>
       </c>
       <c r="B36" s="4">
@@ -2982,7 +3121,7 @@
       <c r="I36"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="13" t="s">
+      <c r="A37" s="12" t="s">
         <v>35</v>
       </c>
       <c r="B37" s="4">
@@ -2994,7 +3133,7 @@
       <c r="I37"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="13" t="s">
+      <c r="A38" s="12" t="s">
         <v>36</v>
       </c>
       <c r="B38" s="4">
@@ -3006,7 +3145,7 @@
       <c r="I38"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="13" t="s">
+      <c r="A39" s="12" t="s">
         <v>37</v>
       </c>
       <c r="B39" s="4">
@@ -3018,7 +3157,7 @@
       <c r="I39"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="13" t="s">
+      <c r="A40" s="12" t="s">
         <v>38</v>
       </c>
       <c r="B40" s="4">
@@ -3030,7 +3169,7 @@
       <c r="I40"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="13" t="s">
+      <c r="A41" s="12" t="s">
         <v>39</v>
       </c>
       <c r="B41" s="4">
@@ -3042,7 +3181,7 @@
       <c r="I41"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="13" t="s">
+      <c r="A42" s="12" t="s">
         <v>40</v>
       </c>
       <c r="B42" s="4">
@@ -3054,7 +3193,7 @@
       <c r="I42"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="13" t="s">
+      <c r="A43" s="12" t="s">
         <v>41</v>
       </c>
       <c r="B43" s="4">
@@ -3066,7 +3205,7 @@
       <c r="I43"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="13" t="s">
+      <c r="A44" s="12" t="s">
         <v>42</v>
       </c>
       <c r="B44" s="4">
@@ -3078,7 +3217,7 @@
       <c r="I44"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="13" t="s">
+      <c r="A45" s="12" t="s">
         <v>43</v>
       </c>
       <c r="B45" s="4">
@@ -3090,7 +3229,7 @@
       <c r="I45"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="13" t="s">
+      <c r="A46" s="12" t="s">
         <v>44</v>
       </c>
       <c r="B46" s="4">
@@ -3102,7 +3241,7 @@
       <c r="I46"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="13" t="s">
+      <c r="A47" s="12" t="s">
         <v>45</v>
       </c>
       <c r="B47" s="4">
@@ -3114,7 +3253,7 @@
       <c r="I47"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="13" t="s">
+      <c r="A48" s="12" t="s">
         <v>46</v>
       </c>
       <c r="B48" s="4">
@@ -3126,7 +3265,7 @@
       <c r="I48"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="13" t="s">
+      <c r="A49" s="12" t="s">
         <v>47</v>
       </c>
       <c r="B49" s="4">
@@ -3138,7 +3277,7 @@
       <c r="I49"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="13" t="s">
+      <c r="A50" s="12" t="s">
         <v>48</v>
       </c>
       <c r="B50" s="4">
@@ -3150,7 +3289,7 @@
       <c r="I50"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="13" t="s">
+      <c r="A51" s="12" t="s">
         <v>49</v>
       </c>
       <c r="B51" s="4">
@@ -3162,7 +3301,7 @@
       <c r="I51"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="13" t="s">
+      <c r="A52" s="12" t="s">
         <v>50</v>
       </c>
       <c r="B52" s="4">
@@ -3174,7 +3313,7 @@
       <c r="I52"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="13" t="s">
+      <c r="A53" s="12" t="s">
         <v>51</v>
       </c>
       <c r="B53" s="4">
@@ -3186,7 +3325,7 @@
       <c r="I53"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="13" t="s">
+      <c r="A54" s="12" t="s">
         <v>52</v>
       </c>
       <c r="B54" s="4">
@@ -3198,7 +3337,7 @@
       <c r="I54"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="13" t="s">
+      <c r="A55" s="12" t="s">
         <v>53</v>
       </c>
       <c r="B55" s="4">
@@ -3210,7 +3349,7 @@
       <c r="I55"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="13" t="s">
+      <c r="A56" s="12" t="s">
         <v>54</v>
       </c>
       <c r="B56" s="4">
@@ -3222,7 +3361,7 @@
       <c r="I56"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="13" t="s">
+      <c r="A57" s="12" t="s">
         <v>55</v>
       </c>
       <c r="B57" s="4">
@@ -3234,7 +3373,7 @@
       <c r="I57"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="13" t="s">
+      <c r="A58" s="12" t="s">
         <v>56</v>
       </c>
       <c r="B58" s="4">
@@ -3246,7 +3385,7 @@
       <c r="I58"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="13" t="s">
+      <c r="A59" s="12" t="s">
         <v>57</v>
       </c>
       <c r="B59" s="4">
@@ -3258,7 +3397,7 @@
       <c r="I59"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="13" t="s">
+      <c r="A60" s="12" t="s">
         <v>58</v>
       </c>
       <c r="B60" s="4">
@@ -3270,7 +3409,7 @@
       <c r="I60"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="13" t="s">
+      <c r="A61" s="12" t="s">
         <v>59</v>
       </c>
       <c r="B61" s="4">
@@ -3282,7 +3421,7 @@
       <c r="I61"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="13" t="s">
+      <c r="A62" s="12" t="s">
         <v>60</v>
       </c>
       <c r="B62" s="4">
@@ -3294,7 +3433,7 @@
       <c r="I62"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="13" t="s">
+      <c r="A63" s="12" t="s">
         <v>61</v>
       </c>
       <c r="B63" s="4">
@@ -3306,7 +3445,7 @@
       <c r="I63"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="13" t="s">
+      <c r="A64" s="12" t="s">
         <v>62</v>
       </c>
       <c r="B64" s="4">
@@ -3318,7 +3457,7 @@
       <c r="I64"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="13" t="s">
+      <c r="A65" s="12" t="s">
         <v>63</v>
       </c>
       <c r="B65" s="4">
@@ -3330,7 +3469,7 @@
       <c r="I65"/>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="13" t="s">
+      <c r="A66" s="12" t="s">
         <v>64</v>
       </c>
       <c r="B66" s="4">
@@ -3342,7 +3481,7 @@
       <c r="I66"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="13" t="s">
+      <c r="A67" s="12" t="s">
         <v>65</v>
       </c>
       <c r="B67" s="4">
@@ -3354,7 +3493,7 @@
       <c r="I67"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="13" t="s">
+      <c r="A68" s="12" t="s">
         <v>66</v>
       </c>
       <c r="B68" s="4">
@@ -3366,7 +3505,7 @@
       <c r="I68"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" s="13" t="s">
+      <c r="A69" s="12" t="s">
         <v>489</v>
       </c>
       <c r="B69" s="2">
@@ -3378,7 +3517,7 @@
       <c r="I69"/>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="13" t="s">
+      <c r="A70" s="12" t="s">
         <v>490</v>
       </c>
       <c r="B70" s="2">
@@ -3390,7 +3529,7 @@
       <c r="I70"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" s="13" t="s">
+      <c r="A71" s="12" t="s">
         <v>491</v>
       </c>
       <c r="B71" s="2">
@@ -3402,7 +3541,7 @@
       <c r="I71"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72" s="13" t="s">
+      <c r="A72" s="12" t="s">
         <v>492</v>
       </c>
       <c r="B72" s="2">
@@ -3414,7 +3553,7 @@
       <c r="I72"/>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" s="13" t="s">
+      <c r="A73" s="12" t="s">
         <v>493</v>
       </c>
       <c r="B73" s="2">
@@ -3426,7 +3565,7 @@
       <c r="I73"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" s="13" t="s">
+      <c r="A74" s="12" t="s">
         <v>494</v>
       </c>
       <c r="B74" s="2">
@@ -3438,7 +3577,7 @@
       <c r="I74"/>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A75" s="13" t="s">
+      <c r="A75" s="12" t="s">
         <v>495</v>
       </c>
       <c r="B75" s="2">
@@ -3450,7 +3589,7 @@
       <c r="I75"/>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A76" s="13" t="s">
+      <c r="A76" s="12" t="s">
         <v>496</v>
       </c>
       <c r="B76" s="2">
@@ -3462,7 +3601,7 @@
       <c r="I76"/>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A77" s="13" t="s">
+      <c r="A77" s="12" t="s">
         <v>497</v>
       </c>
       <c r="B77" s="2">
@@ -3474,7 +3613,7 @@
       <c r="I77"/>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" s="13" t="s">
+      <c r="A78" s="12" t="s">
         <v>498</v>
       </c>
       <c r="B78" s="2">
@@ -3486,7 +3625,7 @@
       <c r="I78"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" s="13" t="s">
+      <c r="A79" s="12" t="s">
         <v>499</v>
       </c>
       <c r="B79" s="2">
@@ -3498,7 +3637,7 @@
       <c r="I79"/>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A80" s="13" t="s">
+      <c r="A80" s="12" t="s">
         <v>500</v>
       </c>
       <c r="B80" s="2">
@@ -3510,7 +3649,7 @@
       <c r="I80"/>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" s="13" t="s">
+      <c r="A81" s="12" t="s">
         <v>501</v>
       </c>
       <c r="B81" s="2">
@@ -3522,7 +3661,7 @@
       <c r="I81"/>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A82" s="13" t="s">
+      <c r="A82" s="12" t="s">
         <v>502</v>
       </c>
       <c r="B82" s="2">
@@ -3534,7 +3673,7 @@
       <c r="I82"/>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A83" s="13" t="s">
+      <c r="A83" s="12" t="s">
         <v>503</v>
       </c>
       <c r="B83" s="2">
@@ -3546,7 +3685,7 @@
       <c r="I83"/>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A84" s="13" t="s">
+      <c r="A84" s="12" t="s">
         <v>504</v>
       </c>
       <c r="B84" s="2">
@@ -3558,7 +3697,7 @@
       <c r="I84"/>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A85" s="13" t="s">
+      <c r="A85" s="12" t="s">
         <v>505</v>
       </c>
       <c r="B85" s="2">
@@ -3570,7 +3709,7 @@
       <c r="I85"/>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A86" s="13" t="s">
+      <c r="A86" s="12" t="s">
         <v>506</v>
       </c>
       <c r="B86" s="2">
@@ -3582,7 +3721,7 @@
       <c r="I86"/>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A87" s="13" t="s">
+      <c r="A87" s="12" t="s">
         <v>507</v>
       </c>
       <c r="B87" s="2">
@@ -3594,7 +3733,7 @@
       <c r="I87"/>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A88" s="13" t="s">
+      <c r="A88" s="12" t="s">
         <v>508</v>
       </c>
       <c r="B88" s="2">
@@ -3606,7 +3745,7 @@
       <c r="I88"/>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A89" s="13" t="s">
+      <c r="A89" s="12" t="s">
         <v>509</v>
       </c>
       <c r="B89" s="2">
@@ -3618,7 +3757,7 @@
       <c r="I89"/>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90" s="13" t="s">
+      <c r="A90" s="12" t="s">
         <v>510</v>
       </c>
       <c r="B90" s="2">
@@ -3630,7 +3769,7 @@
       <c r="I90"/>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A91" s="13" t="s">
+      <c r="A91" s="12" t="s">
         <v>511</v>
       </c>
       <c r="B91" s="2">
@@ -3642,7 +3781,7 @@
       <c r="I91"/>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A92" s="13" t="s">
+      <c r="A92" s="12" t="s">
         <v>512</v>
       </c>
       <c r="B92" s="2">
@@ -3654,7 +3793,7 @@
       <c r="I92"/>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A93" s="13" t="s">
+      <c r="A93" s="12" t="s">
         <v>513</v>
       </c>
       <c r="B93" s="2">
@@ -3666,7 +3805,7 @@
       <c r="I93"/>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A94" s="13" t="s">
+      <c r="A94" s="12" t="s">
         <v>514</v>
       </c>
       <c r="B94" s="2">
@@ -3678,7 +3817,7 @@
       <c r="I94"/>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A95" s="13" t="s">
+      <c r="A95" s="12" t="s">
         <v>515</v>
       </c>
       <c r="B95" s="2">
@@ -3690,7 +3829,7 @@
       <c r="I95"/>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96" s="13" t="s">
+      <c r="A96" s="12" t="s">
         <v>516</v>
       </c>
       <c r="B96" s="2">
@@ -3702,7 +3841,7 @@
       <c r="I96"/>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A97" s="13" t="s">
+      <c r="A97" s="12" t="s">
         <v>517</v>
       </c>
       <c r="B97" s="2">
@@ -3714,7 +3853,7 @@
       <c r="I97"/>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A98" s="13" t="s">
+      <c r="A98" s="12" t="s">
         <v>518</v>
       </c>
       <c r="B98" s="2">
@@ -3726,7 +3865,7 @@
       <c r="I98"/>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A99" s="13" t="s">
+      <c r="A99" s="12" t="s">
         <v>519</v>
       </c>
       <c r="B99" s="2">
@@ -3738,7 +3877,7 @@
       <c r="I99"/>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A100" s="13" t="s">
+      <c r="A100" s="12" t="s">
         <v>520</v>
       </c>
       <c r="B100" s="2">
@@ -3750,7 +3889,7 @@
       <c r="I100"/>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A101" s="13" t="s">
+      <c r="A101" s="12" t="s">
         <v>521</v>
       </c>
       <c r="B101" s="2">
@@ -3762,7 +3901,7 @@
       <c r="I101"/>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A102" s="13" t="s">
+      <c r="A102" s="12" t="s">
         <v>522</v>
       </c>
       <c r="B102" s="2">
@@ -3774,7 +3913,7 @@
       <c r="I102"/>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A103" s="13" t="s">
+      <c r="A103" s="12" t="s">
         <v>523</v>
       </c>
       <c r="B103" s="2">
@@ -3786,7 +3925,7 @@
       <c r="I103"/>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A104" s="13" t="s">
+      <c r="A104" s="12" t="s">
         <v>524</v>
       </c>
       <c r="B104" s="2">
@@ -3798,7 +3937,7 @@
       <c r="I104"/>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A105" s="13" t="s">
+      <c r="A105" s="12" t="s">
         <v>525</v>
       </c>
       <c r="B105" s="2">
@@ -3810,7 +3949,7 @@
       <c r="I105"/>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A106" s="13" t="s">
+      <c r="A106" s="12" t="s">
         <v>526</v>
       </c>
       <c r="B106" s="2">
@@ -3822,7 +3961,7 @@
       <c r="I106"/>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A107" s="13" t="s">
+      <c r="A107" s="12" t="s">
         <v>527</v>
       </c>
       <c r="B107" s="2">
@@ -3834,7 +3973,7 @@
       <c r="I107"/>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A108" s="13" t="s">
+      <c r="A108" s="12" t="s">
         <v>528</v>
       </c>
       <c r="B108" s="2">
@@ -3846,7 +3985,7 @@
       <c r="I108"/>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A109" s="13" t="s">
+      <c r="A109" s="12" t="s">
         <v>529</v>
       </c>
       <c r="B109" s="2">
@@ -3858,7 +3997,7 @@
       <c r="I109"/>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A110" s="13" t="s">
+      <c r="A110" s="12" t="s">
         <v>530</v>
       </c>
       <c r="B110" s="2">
@@ -3870,7 +4009,7 @@
       <c r="I110"/>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A111" s="13" t="s">
+      <c r="A111" s="12" t="s">
         <v>531</v>
       </c>
       <c r="B111" s="2">
@@ -3882,7 +4021,7 @@
       <c r="I111"/>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A112" s="13" t="s">
+      <c r="A112" s="12" t="s">
         <v>532</v>
       </c>
       <c r="B112" s="2">
@@ -3894,7 +4033,7 @@
       <c r="I112"/>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A113" s="13" t="s">
+      <c r="A113" s="12" t="s">
         <v>533</v>
       </c>
       <c r="B113" s="2">
@@ -3906,7 +4045,7 @@
       <c r="I113"/>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A114" s="13" t="s">
+      <c r="A114" s="12" t="s">
         <v>534</v>
       </c>
       <c r="B114" s="2">
@@ -3918,7 +4057,7 @@
       <c r="I114"/>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A115" s="13" t="s">
+      <c r="A115" s="12" t="s">
         <v>535</v>
       </c>
       <c r="B115" s="2">
@@ -3930,7 +4069,7 @@
       <c r="I115"/>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A116" s="13" t="s">
+      <c r="A116" s="12" t="s">
         <v>536</v>
       </c>
       <c r="B116" s="2">
@@ -3942,7 +4081,7 @@
       <c r="I116"/>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A117" s="13" t="s">
+      <c r="A117" s="12" t="s">
         <v>537</v>
       </c>
       <c r="B117" s="2">
@@ -3954,7 +4093,7 @@
       <c r="I117"/>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A118" s="13" t="s">
+      <c r="A118" s="12" t="s">
         <v>538</v>
       </c>
       <c r="B118" s="2">
@@ -3966,7 +4105,7 @@
       <c r="I118"/>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A119" s="13" t="s">
+      <c r="A119" s="12" t="s">
         <v>539</v>
       </c>
       <c r="B119" s="2">
@@ -3978,7 +4117,7 @@
       <c r="I119"/>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A120" s="13" t="s">
+      <c r="A120" s="12" t="s">
         <v>540</v>
       </c>
       <c r="B120" s="2">
@@ -3990,7 +4129,7 @@
       <c r="I120"/>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A121" s="13" t="s">
+      <c r="A121" s="12" t="s">
         <v>541</v>
       </c>
       <c r="B121" s="2">
@@ -4002,7 +4141,7 @@
       <c r="I121"/>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A122" s="13" t="s">
+      <c r="A122" s="12" t="s">
         <v>542</v>
       </c>
       <c r="B122" s="2">
@@ -4014,7 +4153,7 @@
       <c r="I122"/>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A123" s="13" t="s">
+      <c r="A123" s="12" t="s">
         <v>543</v>
       </c>
       <c r="B123" s="2">
@@ -4026,7 +4165,7 @@
       <c r="I123"/>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A124" s="13" t="s">
+      <c r="A124" s="12" t="s">
         <v>544</v>
       </c>
       <c r="B124" s="2">
@@ -4038,7 +4177,7 @@
       <c r="I124"/>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A125" s="13" t="s">
+      <c r="A125" s="12" t="s">
         <v>545</v>
       </c>
       <c r="B125" s="2">
@@ -4050,7 +4189,7 @@
       <c r="I125"/>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A126" s="13" t="s">
+      <c r="A126" s="12" t="s">
         <v>546</v>
       </c>
       <c r="B126" s="2">
@@ -4062,7 +4201,7 @@
       <c r="I126"/>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A127" s="13" t="s">
+      <c r="A127" s="12" t="s">
         <v>547</v>
       </c>
       <c r="B127" s="2">
@@ -4074,7 +4213,7 @@
       <c r="I127"/>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A128" s="13" t="s">
+      <c r="A128" s="12" t="s">
         <v>548</v>
       </c>
       <c r="B128" s="2">
@@ -4086,7 +4225,7 @@
       <c r="I128"/>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A129" s="13" t="s">
+      <c r="A129" s="12" t="s">
         <v>549</v>
       </c>
       <c r="B129" s="2">
@@ -4098,7 +4237,7 @@
       <c r="I129"/>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A130" s="13" t="s">
+      <c r="A130" s="12" t="s">
         <v>550</v>
       </c>
       <c r="B130" s="2">
@@ -4110,7 +4249,7 @@
       <c r="I130"/>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A131" s="13" t="s">
+      <c r="A131" s="12" t="s">
         <v>551</v>
       </c>
       <c r="B131" s="2">
@@ -4122,7 +4261,7 @@
       <c r="I131"/>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A132" s="13" t="s">
+      <c r="A132" s="12" t="s">
         <v>552</v>
       </c>
       <c r="B132" s="2">
@@ -4134,7 +4273,7 @@
       <c r="I132"/>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A133" s="13" t="s">
+      <c r="A133" s="12" t="s">
         <v>553</v>
       </c>
       <c r="B133" s="2">
@@ -4146,7 +4285,7 @@
       <c r="I133"/>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A134" s="13" t="s">
+      <c r="A134" s="12" t="s">
         <v>554</v>
       </c>
       <c r="B134" s="2">
@@ -4158,7 +4297,7 @@
       <c r="I134"/>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A135" s="13" t="s">
+      <c r="A135" s="12" t="s">
         <v>555</v>
       </c>
       <c r="B135" s="2">
@@ -4170,7 +4309,7 @@
       <c r="I135"/>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A136" s="13" t="s">
+      <c r="A136" s="12" t="s">
         <v>556</v>
       </c>
       <c r="B136" s="2">
@@ -4182,7 +4321,7 @@
       <c r="I136"/>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A137" s="13" t="s">
+      <c r="A137" s="12" t="s">
         <v>557</v>
       </c>
       <c r="B137" s="2">
@@ -4194,7 +4333,7 @@
       <c r="I137"/>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A138" s="13" t="s">
+      <c r="A138" s="12" t="s">
         <v>558</v>
       </c>
       <c r="B138" s="2">
@@ -4206,7 +4345,7 @@
       <c r="I138"/>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A139" s="13" t="s">
+      <c r="A139" s="12" t="s">
         <v>559</v>
       </c>
       <c r="B139" s="2">
@@ -4218,7 +4357,7 @@
       <c r="I139"/>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A140" s="13" t="s">
+      <c r="A140" s="12" t="s">
         <v>560</v>
       </c>
       <c r="B140" s="2">
@@ -4230,7 +4369,7 @@
       <c r="I140"/>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A141" s="13" t="s">
+      <c r="A141" s="12" t="s">
         <v>561</v>
       </c>
       <c r="B141" s="2">
@@ -4242,7 +4381,7 @@
       <c r="I141"/>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A142" s="13" t="s">
+      <c r="A142" s="12" t="s">
         <v>562</v>
       </c>
       <c r="B142" s="2">
@@ -4254,7 +4393,7 @@
       <c r="I142"/>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A143" s="13" t="s">
+      <c r="A143" s="12" t="s">
         <v>563</v>
       </c>
       <c r="B143" s="2">
@@ -4266,7 +4405,7 @@
       <c r="I143"/>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A144" s="13" t="s">
+      <c r="A144" s="12" t="s">
         <v>564</v>
       </c>
       <c r="B144" s="2">
@@ -4278,7 +4417,7 @@
       <c r="I144"/>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A145" s="13" t="s">
+      <c r="A145" s="12" t="s">
         <v>565</v>
       </c>
       <c r="B145" s="2">
@@ -4290,7 +4429,7 @@
       <c r="I145"/>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A146" s="13" t="s">
+      <c r="A146" s="12" t="s">
         <v>566</v>
       </c>
       <c r="B146" s="2">
@@ -4302,7 +4441,7 @@
       <c r="I146"/>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A147" s="13" t="s">
+      <c r="A147" s="12" t="s">
         <v>567</v>
       </c>
       <c r="B147" s="2">
@@ -4314,7 +4453,7 @@
       <c r="I147"/>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A148" s="13" t="s">
+      <c r="A148" s="12" t="s">
         <v>568</v>
       </c>
       <c r="B148" s="2">
@@ -4326,7 +4465,7 @@
       <c r="I148"/>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A149" s="13" t="s">
+      <c r="A149" s="12" t="s">
         <v>569</v>
       </c>
       <c r="B149" s="2">
@@ -4338,7 +4477,7 @@
       <c r="I149"/>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A150" s="13" t="s">
+      <c r="A150" s="12" t="s">
         <v>570</v>
       </c>
       <c r="B150" s="2">
@@ -4350,7 +4489,7 @@
       <c r="I150"/>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A151" s="13" t="s">
+      <c r="A151" s="12" t="s">
         <v>571</v>
       </c>
       <c r="B151" s="2">
@@ -4362,7 +4501,7 @@
       <c r="I151"/>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A152" s="13" t="s">
+      <c r="A152" s="12" t="s">
         <v>572</v>
       </c>
       <c r="B152" s="2">
@@ -4374,7 +4513,7 @@
       <c r="I152"/>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A153" s="13" t="s">
+      <c r="A153" s="12" t="s">
         <v>573</v>
       </c>
       <c r="B153" s="2">
@@ -4386,7 +4525,7 @@
       <c r="I153"/>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A154" s="13" t="s">
+      <c r="A154" s="12" t="s">
         <v>574</v>
       </c>
       <c r="B154" s="2">
@@ -4398,7 +4537,7 @@
       <c r="I154"/>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A155" s="13" t="s">
+      <c r="A155" s="12" t="s">
         <v>575</v>
       </c>
       <c r="B155" s="2">
@@ -4410,7 +4549,7 @@
       <c r="I155"/>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A156" s="13" t="s">
+      <c r="A156" s="12" t="s">
         <v>576</v>
       </c>
       <c r="B156" s="2">
@@ -4422,7 +4561,7 @@
       <c r="I156"/>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A157" s="13" t="s">
+      <c r="A157" s="12" t="s">
         <v>577</v>
       </c>
       <c r="B157" s="2">
@@ -4434,7 +4573,7 @@
       <c r="I157"/>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A158" s="13" t="s">
+      <c r="A158" s="12" t="s">
         <v>578</v>
       </c>
       <c r="B158" s="2">
@@ -4446,7 +4585,7 @@
       <c r="I158"/>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A159" s="13" t="s">
+      <c r="A159" s="12" t="s">
         <v>579</v>
       </c>
       <c r="B159" s="2">
@@ -4458,7 +4597,7 @@
       <c r="I159"/>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A160" s="13" t="s">
+      <c r="A160" s="12" t="s">
         <v>580</v>
       </c>
       <c r="B160" s="2">
@@ -4470,7 +4609,7 @@
       <c r="I160"/>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A161" s="13" t="s">
+      <c r="A161" s="12" t="s">
         <v>581</v>
       </c>
       <c r="B161" s="2">
@@ -4482,7 +4621,7 @@
       <c r="I161"/>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A162" s="13" t="s">
+      <c r="A162" s="12" t="s">
         <v>582</v>
       </c>
       <c r="B162" s="2">
@@ -4494,7 +4633,7 @@
       <c r="I162"/>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A163" s="13" t="s">
+      <c r="A163" s="12" t="s">
         <v>583</v>
       </c>
       <c r="B163" s="2">
@@ -4506,7 +4645,7 @@
       <c r="I163"/>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A164" s="13" t="s">
+      <c r="A164" s="12" t="s">
         <v>584</v>
       </c>
       <c r="B164" s="2">
@@ -4518,7 +4657,7 @@
       <c r="I164"/>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A165" s="13" t="s">
+      <c r="A165" s="12" t="s">
         <v>585</v>
       </c>
       <c r="B165" s="2">
@@ -4530,7 +4669,7 @@
       <c r="I165"/>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A166" s="13" t="s">
+      <c r="A166" s="12" t="s">
         <v>586</v>
       </c>
       <c r="B166" s="2">
@@ -4542,7 +4681,7 @@
       <c r="I166"/>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A167" s="13" t="s">
+      <c r="A167" s="12" t="s">
         <v>587</v>
       </c>
       <c r="B167" s="2">
@@ -4554,7 +4693,7 @@
       <c r="I167"/>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A168" s="13" t="s">
+      <c r="A168" s="12" t="s">
         <v>67</v>
       </c>
       <c r="B168" s="2">
@@ -4566,7 +4705,7 @@
       <c r="I168"/>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A169" s="13" t="s">
+      <c r="A169" s="12" t="s">
         <v>68</v>
       </c>
       <c r="B169" s="2">
@@ -4578,7 +4717,7 @@
       <c r="I169"/>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A170" s="13" t="s">
+      <c r="A170" s="12" t="s">
         <v>447</v>
       </c>
       <c r="B170" s="2">
@@ -4590,7 +4729,7 @@
       <c r="I170"/>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A171" s="13" t="s">
+      <c r="A171" s="12" t="s">
         <v>69</v>
       </c>
       <c r="B171" s="2">
@@ -4602,7 +4741,7 @@
       <c r="I171"/>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A172" s="13" t="s">
+      <c r="A172" s="12" t="s">
         <v>70</v>
       </c>
       <c r="B172" s="2">
@@ -4614,7 +4753,7 @@
       <c r="I172"/>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A173" s="13" t="s">
+      <c r="A173" s="12" t="s">
         <v>71</v>
       </c>
       <c r="B173" s="2">
@@ -4626,7 +4765,7 @@
       <c r="I173"/>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A174" s="13" t="s">
+      <c r="A174" s="12" t="s">
         <v>72</v>
       </c>
       <c r="B174" s="2">
@@ -4638,7 +4777,7 @@
       <c r="I174"/>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A175" s="13" t="s">
+      <c r="A175" s="12" t="s">
         <v>73</v>
       </c>
       <c r="B175" s="2">
@@ -4650,7 +4789,7 @@
       <c r="I175"/>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A176" s="13" t="s">
+      <c r="A176" s="12" t="s">
         <v>74</v>
       </c>
       <c r="B176" s="2">
@@ -4662,7 +4801,7 @@
       <c r="I176"/>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A177" s="13" t="s">
+      <c r="A177" s="12" t="s">
         <v>75</v>
       </c>
       <c r="B177" s="2">
@@ -4674,7 +4813,7 @@
       <c r="I177"/>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A178" s="13" t="s">
+      <c r="A178" s="12" t="s">
         <v>76</v>
       </c>
       <c r="B178" s="2">
@@ -4686,7 +4825,7 @@
       <c r="I178"/>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A179" s="13" t="s">
+      <c r="A179" s="12" t="s">
         <v>77</v>
       </c>
       <c r="B179" s="2">
@@ -4698,7 +4837,7 @@
       <c r="I179"/>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A180" s="13" t="s">
+      <c r="A180" s="12" t="s">
         <v>78</v>
       </c>
       <c r="B180" s="2">
@@ -4710,7 +4849,7 @@
       <c r="I180"/>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A181" s="13" t="s">
+      <c r="A181" s="12" t="s">
         <v>79</v>
       </c>
       <c r="B181" s="2">
@@ -4722,7 +4861,7 @@
       <c r="I181"/>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A182" s="13" t="s">
+      <c r="A182" s="12" t="s">
         <v>620</v>
       </c>
       <c r="B182" s="2">
@@ -4734,7 +4873,7 @@
       <c r="I182"/>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A183" s="13" t="s">
+      <c r="A183" s="12" t="s">
         <v>80</v>
       </c>
       <c r="B183" s="2">
@@ -4746,7 +4885,7 @@
       <c r="I183"/>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A184" s="13" t="s">
+      <c r="A184" s="12" t="s">
         <v>81</v>
       </c>
       <c r="B184" s="2">
@@ -4758,7 +4897,7 @@
       <c r="I184"/>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A185" s="13" t="s">
+      <c r="A185" s="12" t="s">
         <v>82</v>
       </c>
       <c r="B185" s="2">
@@ -4770,7 +4909,7 @@
       <c r="I185"/>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A186" s="13" t="s">
+      <c r="A186" s="12" t="s">
         <v>83</v>
       </c>
       <c r="B186" s="2">
@@ -4782,7 +4921,7 @@
       <c r="I186"/>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A187" s="13" t="s">
+      <c r="A187" s="12" t="s">
         <v>472</v>
       </c>
       <c r="C187" s="2">
@@ -4791,7 +4930,7 @@
       <c r="I187"/>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A188" s="13" t="s">
+      <c r="A188" s="12" t="s">
         <v>483</v>
       </c>
       <c r="C188" s="2">
@@ -4800,7 +4939,7 @@
       <c r="I188"/>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A189" s="13" t="s">
+      <c r="A189" s="12" t="s">
         <v>486</v>
       </c>
       <c r="C189" s="2">
@@ -4809,7 +4948,7 @@
       <c r="I189"/>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A190" s="13" t="s">
+      <c r="A190" s="12" t="s">
         <v>454</v>
       </c>
       <c r="C190" s="2">
@@ -4818,7 +4957,7 @@
       <c r="I190"/>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A191" s="13" t="s">
+      <c r="A191" s="12" t="s">
         <v>478</v>
       </c>
       <c r="C191" s="2">
@@ -4827,7 +4966,7 @@
       <c r="I191"/>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A192" s="13" t="s">
+      <c r="A192" s="12" t="s">
         <v>473</v>
       </c>
       <c r="C192" s="2">
@@ -4836,7 +4975,7 @@
       <c r="I192"/>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A193" s="13" t="s">
+      <c r="A193" s="12" t="s">
         <v>475</v>
       </c>
       <c r="C193" s="2">
@@ -4845,7 +4984,7 @@
       <c r="I193"/>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A194" s="13" t="s">
+      <c r="A194" s="12" t="s">
         <v>455</v>
       </c>
       <c r="C194" s="2">
@@ -4854,7 +4993,7 @@
       <c r="I194"/>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A195" s="13" t="s">
+      <c r="A195" s="12" t="s">
         <v>451</v>
       </c>
       <c r="C195" s="2">
@@ -4863,7 +5002,7 @@
       <c r="I195"/>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A196" s="13" t="s">
+      <c r="A196" s="12" t="s">
         <v>471</v>
       </c>
       <c r="C196" s="2">
@@ -4872,7 +5011,7 @@
       <c r="I196"/>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A197" s="13" t="s">
+      <c r="A197" s="12" t="s">
         <v>466</v>
       </c>
       <c r="C197" s="2">
@@ -4881,7 +5020,7 @@
       <c r="I197"/>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A198" s="13" t="s">
+      <c r="A198" s="12" t="s">
         <v>484</v>
       </c>
       <c r="C198" s="2">
@@ -4890,7 +5029,7 @@
       <c r="I198"/>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A199" s="13" t="s">
+      <c r="A199" s="12" t="s">
         <v>456</v>
       </c>
       <c r="C199" s="2">
@@ -4899,7 +5038,7 @@
       <c r="I199"/>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A200" s="13" t="s">
+      <c r="A200" s="12" t="s">
         <v>470</v>
       </c>
       <c r="C200" s="2">
@@ -4908,7 +5047,7 @@
       <c r="I200"/>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A201" s="13" t="s">
+      <c r="A201" s="12" t="s">
         <v>469</v>
       </c>
       <c r="C201" s="2">
@@ -4917,7 +5056,7 @@
       <c r="I201"/>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A202" s="13" t="s">
+      <c r="A202" s="12" t="s">
         <v>465</v>
       </c>
       <c r="C202" s="2">
@@ -4926,7 +5065,7 @@
       <c r="I202"/>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A203" s="13" t="s">
+      <c r="A203" s="12" t="s">
         <v>467</v>
       </c>
       <c r="C203" s="2">
@@ -4935,7 +5074,7 @@
       <c r="I203"/>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A204" s="13" t="s">
+      <c r="A204" s="12" t="s">
         <v>453</v>
       </c>
       <c r="C204" s="2">
@@ -4944,7 +5083,7 @@
       <c r="I204"/>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A205" s="13" t="s">
+      <c r="A205" s="12" t="s">
         <v>487</v>
       </c>
       <c r="C205" s="2">
@@ -4953,7 +5092,7 @@
       <c r="I205"/>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A206" s="13" t="s">
+      <c r="A206" s="12" t="s">
         <v>452</v>
       </c>
       <c r="C206" s="2">
@@ -4962,7 +5101,7 @@
       <c r="I206"/>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A207" s="13" t="s">
+      <c r="A207" s="12" t="s">
         <v>461</v>
       </c>
       <c r="C207" s="2">
@@ -4971,7 +5110,7 @@
       <c r="I207"/>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A208" s="13" t="s">
+      <c r="A208" s="12" t="s">
         <v>460</v>
       </c>
       <c r="C208" s="2">
@@ -4980,7 +5119,7 @@
       <c r="I208"/>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A209" s="13" t="s">
+      <c r="A209" s="12" t="s">
         <v>463</v>
       </c>
       <c r="C209" s="2">
@@ -4989,7 +5128,7 @@
       <c r="I209"/>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A210" s="13" t="s">
+      <c r="A210" s="12" t="s">
         <v>474</v>
       </c>
       <c r="C210" s="2">
@@ -4998,7 +5137,7 @@
       <c r="I210"/>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A211" s="13" t="s">
+      <c r="A211" s="12" t="s">
         <v>477</v>
       </c>
       <c r="C211" s="2">
@@ -5007,7 +5146,7 @@
       <c r="I211"/>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A212" s="13" t="s">
+      <c r="A212" s="12" t="s">
         <v>459</v>
       </c>
       <c r="C212" s="2">
@@ -5016,7 +5155,7 @@
       <c r="I212"/>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A213" s="13" t="s">
+      <c r="A213" s="12" t="s">
         <v>464</v>
       </c>
       <c r="C213" s="2">
@@ -5025,7 +5164,7 @@
       <c r="I213"/>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A214" s="13" t="s">
+      <c r="A214" s="12" t="s">
         <v>458</v>
       </c>
       <c r="C214" s="2">
@@ -5034,7 +5173,7 @@
       <c r="I214"/>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A215" s="13" t="s">
+      <c r="A215" s="12" t="s">
         <v>462</v>
       </c>
       <c r="C215" s="2">
@@ -5043,7 +5182,7 @@
       <c r="I215"/>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A216" s="13" t="s">
+      <c r="A216" s="12" t="s">
         <v>485</v>
       </c>
       <c r="C216" s="2">
@@ -5052,7 +5191,7 @@
       <c r="I216"/>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A217" s="13" t="s">
+      <c r="A217" s="12" t="s">
         <v>457</v>
       </c>
       <c r="C217" s="2">
@@ -5061,7 +5200,7 @@
       <c r="I217"/>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A218" s="13" t="s">
+      <c r="A218" s="12" t="s">
         <v>468</v>
       </c>
       <c r="C218" s="2">
@@ -5070,7 +5209,7 @@
       <c r="I218"/>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A219" s="13" t="s">
+      <c r="A219" s="12" t="s">
         <v>480</v>
       </c>
       <c r="C219" s="2">
@@ -5079,7 +5218,7 @@
       <c r="I219"/>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A220" s="13" t="s">
+      <c r="A220" s="12" t="s">
         <v>479</v>
       </c>
       <c r="C220" s="2">
@@ -5088,7 +5227,7 @@
       <c r="I220"/>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A221" s="13" t="s">
+      <c r="A221" s="12" t="s">
         <v>482</v>
       </c>
       <c r="C221" s="2">
@@ -5097,7 +5236,7 @@
       <c r="I221"/>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A222" s="13" t="s">
+      <c r="A222" s="12" t="s">
         <v>481</v>
       </c>
       <c r="C222" s="2">
@@ -5106,7 +5245,7 @@
       <c r="I222"/>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A223" s="13" t="s">
+      <c r="A223" s="12" t="s">
         <v>476</v>
       </c>
       <c r="C223" s="2">
@@ -5115,7 +5254,7 @@
       <c r="I223"/>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A224" s="13" t="s">
+      <c r="A224" s="12" t="s">
         <v>84</v>
       </c>
       <c r="B224" s="2">
@@ -5127,7 +5266,7 @@
       <c r="I224"/>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A225" s="13" t="s">
+      <c r="A225" s="12" t="s">
         <v>621</v>
       </c>
       <c r="B225" s="2">
@@ -5139,7 +5278,7 @@
       <c r="I225"/>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A226" s="13" t="s">
+      <c r="A226" s="12" t="s">
         <v>85</v>
       </c>
       <c r="B226" s="2">
@@ -5151,7 +5290,7 @@
       <c r="I226"/>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A227" s="13" t="s">
+      <c r="A227" s="12" t="s">
         <v>86</v>
       </c>
       <c r="B227" s="2">
@@ -5163,7 +5302,7 @@
       <c r="I227"/>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A228" s="13" t="s">
+      <c r="A228" s="12" t="s">
         <v>87</v>
       </c>
       <c r="B228" s="2">
@@ -5175,7 +5314,7 @@
       <c r="I228"/>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A229" s="13" t="s">
+      <c r="A229" s="12" t="s">
         <v>622</v>
       </c>
       <c r="B229" s="2">
@@ -5187,7 +5326,7 @@
       <c r="I229"/>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A230" s="13" t="s">
+      <c r="A230" s="12" t="s">
         <v>448</v>
       </c>
       <c r="B230" s="2">
@@ -5199,7 +5338,7 @@
       <c r="I230"/>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A231" s="13" t="s">
+      <c r="A231" s="12" t="s">
         <v>446</v>
       </c>
       <c r="B231" s="2">
@@ -5211,7 +5350,7 @@
       <c r="I231"/>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A232" s="13" t="s">
+      <c r="A232" s="12" t="s">
         <v>88</v>
       </c>
       <c r="B232" s="2">
@@ -5223,7 +5362,7 @@
       <c r="I232"/>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A233" s="13" t="s">
+      <c r="A233" s="12" t="s">
         <v>89</v>
       </c>
       <c r="B233" s="2">
@@ -5235,7 +5374,7 @@
       <c r="I233"/>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A234" s="13" t="s">
+      <c r="A234" s="12" t="s">
         <v>90</v>
       </c>
       <c r="B234" s="2">
@@ -5247,7 +5386,7 @@
       <c r="I234"/>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A235" s="13" t="s">
+      <c r="A235" s="12" t="s">
         <v>91</v>
       </c>
       <c r="B235" s="2">
@@ -5259,7 +5398,7 @@
       <c r="I235"/>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A236" s="13" t="s">
+      <c r="A236" s="12" t="s">
         <v>92</v>
       </c>
       <c r="B236" s="2">
@@ -5271,7 +5410,7 @@
       <c r="I236"/>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A237" s="13" t="s">
+      <c r="A237" s="12" t="s">
         <v>93</v>
       </c>
       <c r="B237" s="2">
@@ -5283,7 +5422,7 @@
       <c r="I237"/>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A238" s="13" t="s">
+      <c r="A238" s="12" t="s">
         <v>94</v>
       </c>
       <c r="B238" s="2">
@@ -5295,7 +5434,7 @@
       <c r="I238"/>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A239" s="13" t="s">
+      <c r="A239" s="12" t="s">
         <v>95</v>
       </c>
       <c r="B239" s="2">
@@ -5307,7 +5446,7 @@
       <c r="I239"/>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A240" s="13" t="s">
+      <c r="A240" s="12" t="s">
         <v>96</v>
       </c>
       <c r="B240" s="2">
@@ -5319,7 +5458,7 @@
       <c r="I240"/>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A241" s="13" t="s">
+      <c r="A241" s="12" t="s">
         <v>97</v>
       </c>
       <c r="B241" s="2">
@@ -5331,7 +5470,7 @@
       <c r="I241"/>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A242" s="13" t="s">
+      <c r="A242" s="12" t="s">
         <v>98</v>
       </c>
       <c r="B242" s="2">
@@ -5342,8 +5481,8 @@
       </c>
       <c r="I242"/>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A243" s="13" t="s">
+    <row r="243" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A243" s="12" t="s">
         <v>99</v>
       </c>
       <c r="B243" s="2">
@@ -5355,1136 +5494,1136 @@
       <c r="I243"/>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A244" s="13" t="s">
+      <c r="A244" s="5" t="s">
+        <v>656</v>
+      </c>
+      <c r="B244" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C244" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I244"/>
+    </row>
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A245" s="5" t="s">
+        <v>657</v>
+      </c>
+      <c r="B245" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C245" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I245"/>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A246" s="5" t="s">
+        <v>658</v>
+      </c>
+      <c r="B246" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C246" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I246"/>
+    </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A247" s="5" t="s">
+        <v>659</v>
+      </c>
+      <c r="B247" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C247" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I247"/>
+    </row>
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A248" s="5" t="s">
+        <v>660</v>
+      </c>
+      <c r="B248" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C248" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I248"/>
+    </row>
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A249" s="5" t="s">
+        <v>661</v>
+      </c>
+      <c r="B249" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C249" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I249"/>
+    </row>
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A250" s="5" t="s">
+        <v>662</v>
+      </c>
+      <c r="B250" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C250" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I250"/>
+    </row>
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A251" s="5" t="s">
+        <v>663</v>
+      </c>
+      <c r="B251" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C251" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I251"/>
+    </row>
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A252" s="5" t="s">
+        <v>664</v>
+      </c>
+      <c r="B252" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C252" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I252"/>
+    </row>
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A253" s="5" t="s">
+        <v>665</v>
+      </c>
+      <c r="B253" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C253" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I253"/>
+    </row>
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A254" s="5" t="s">
+        <v>666</v>
+      </c>
+      <c r="B254" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C254" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I254"/>
+    </row>
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A255" s="5" t="s">
+        <v>667</v>
+      </c>
+      <c r="B255" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C255" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I255"/>
+    </row>
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A256" s="5" t="s">
+        <v>668</v>
+      </c>
+      <c r="B256" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C256" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I256"/>
+    </row>
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A257" s="5" t="s">
+        <v>669</v>
+      </c>
+      <c r="B257" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C257" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I257"/>
+    </row>
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A258" s="5" t="s">
+        <v>670</v>
+      </c>
+      <c r="B258" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C258" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I258"/>
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A259" s="5" t="s">
+        <v>671</v>
+      </c>
+      <c r="B259" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C259" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I259"/>
+    </row>
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A260" s="5" t="s">
+        <v>672</v>
+      </c>
+      <c r="B260" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C260" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I260"/>
+    </row>
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A261" s="5" t="s">
+        <v>673</v>
+      </c>
+      <c r="B261" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C261" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I261"/>
+    </row>
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A262" s="5" t="s">
+        <v>674</v>
+      </c>
+      <c r="B262" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C262" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I262"/>
+    </row>
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A263" s="5" t="s">
+        <v>675</v>
+      </c>
+      <c r="B263" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C263" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I263"/>
+    </row>
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A264" s="5" t="s">
+        <v>676</v>
+      </c>
+      <c r="B264" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C264" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I264"/>
+    </row>
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A265" s="5" t="s">
+        <v>677</v>
+      </c>
+      <c r="B265" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C265" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I265"/>
+    </row>
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A266" s="5" t="s">
+        <v>678</v>
+      </c>
+      <c r="B266" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C266" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I266"/>
+    </row>
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A267" s="5" t="s">
+        <v>679</v>
+      </c>
+      <c r="B267" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C267" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I267"/>
+    </row>
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A268" s="5" t="s">
+        <v>680</v>
+      </c>
+      <c r="B268" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C268" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I268"/>
+    </row>
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A269" s="5" t="s">
+        <v>681</v>
+      </c>
+      <c r="B269" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C269" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I269"/>
+    </row>
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A270" s="5" t="s">
+        <v>682</v>
+      </c>
+      <c r="B270" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C270" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I270"/>
+    </row>
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A271" s="5" t="s">
+        <v>683</v>
+      </c>
+      <c r="B271" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C271" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I271"/>
+    </row>
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A272" s="5" t="s">
+        <v>684</v>
+      </c>
+      <c r="B272" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C272" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I272"/>
+    </row>
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A273" s="5" t="s">
+        <v>685</v>
+      </c>
+      <c r="B273" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C273" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I273"/>
+    </row>
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A274" s="5" t="s">
+        <v>686</v>
+      </c>
+      <c r="B274" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C274" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I274"/>
+    </row>
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A275" s="5" t="s">
+        <v>687</v>
+      </c>
+      <c r="B275" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C275" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I275"/>
+    </row>
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A276" s="5" t="s">
+        <v>688</v>
+      </c>
+      <c r="B276" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C276" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I276"/>
+    </row>
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A277" s="5" t="s">
+        <v>689</v>
+      </c>
+      <c r="B277" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C277" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I277"/>
+    </row>
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A278" s="5" t="s">
+        <v>690</v>
+      </c>
+      <c r="B278" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C278" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I278"/>
+    </row>
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A279" s="5" t="s">
+        <v>691</v>
+      </c>
+      <c r="B279" s="2">
+        <v>11700</v>
+      </c>
+      <c r="C279" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I279"/>
+    </row>
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A280" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="B244" s="4"/>
-      <c r="C244" s="2"/>
-      <c r="I244"/>
-    </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A245" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="B245" s="4"/>
-      <c r="C245" s="2"/>
-      <c r="I245"/>
-    </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A246" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="B246" s="4"/>
-      <c r="C246" s="2"/>
-      <c r="I246"/>
-    </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A247" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="B247" s="4"/>
-      <c r="C247" s="2"/>
-      <c r="I247"/>
-    </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A248" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="B248" s="4"/>
-      <c r="C248" s="2"/>
-      <c r="I248"/>
-    </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A249" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="B249" s="4"/>
-      <c r="C249" s="2"/>
-      <c r="I249"/>
-    </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A250" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="B250" s="4"/>
-      <c r="C250" s="2"/>
-      <c r="I250"/>
-    </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A251" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="B251" s="4"/>
-      <c r="C251" s="2"/>
-      <c r="I251"/>
-    </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A252" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="C252" s="2"/>
-      <c r="I252"/>
-    </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A253" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="C253" s="2"/>
-      <c r="I253"/>
-    </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A254" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="C254" s="2"/>
-      <c r="I254"/>
-    </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A255" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="C255" s="2"/>
-      <c r="I255"/>
-    </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A256" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="C256" s="2"/>
-      <c r="I256"/>
-    </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A257" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="C257" s="2"/>
-      <c r="I257"/>
-    </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A258" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="C258" s="2"/>
-      <c r="I258"/>
-    </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A259" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="C259" s="2"/>
-      <c r="I259"/>
-    </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A260" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="C260" s="2"/>
-      <c r="I260"/>
-    </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A261" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="C261" s="2"/>
-      <c r="I261"/>
-    </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A262" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C262" s="2"/>
-      <c r="I262"/>
-    </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A263" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="C263" s="2"/>
-      <c r="I263"/>
-    </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A264" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="C264" s="2"/>
-      <c r="I264"/>
-    </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A265" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="C265" s="2"/>
-      <c r="I265"/>
-    </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A266" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="C266" s="2"/>
-      <c r="I266"/>
-    </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A267" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="C267" s="2"/>
-      <c r="I267"/>
-    </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A268" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="C268" s="2"/>
-      <c r="I268"/>
-    </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A269" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="C269" s="2"/>
-      <c r="I269"/>
-    </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A270" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="C270" s="2"/>
-      <c r="I270"/>
-    </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A271" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="C271" s="2"/>
-      <c r="I271"/>
-    </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A272" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="C272" s="2"/>
-      <c r="I272"/>
-    </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A273" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="C273" s="2"/>
-      <c r="I273"/>
-    </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A274" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="C274" s="2"/>
-      <c r="I274"/>
-    </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A275" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="C275" s="2"/>
-      <c r="I275"/>
-    </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A276" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="C276" s="2"/>
-      <c r="I276"/>
-    </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A277" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="C277" s="2"/>
-      <c r="I277"/>
-    </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A278" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="C278" s="2"/>
-      <c r="I278"/>
-    </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A279" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="C279" s="2"/>
-      <c r="I279"/>
-    </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A280" s="13" t="s">
-        <v>136</v>
-      </c>
+      <c r="B280" s="4"/>
       <c r="C280" s="2"/>
       <c r="I280"/>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A281" s="13" t="s">
-        <v>137</v>
-      </c>
+      <c r="A281" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="B281" s="4"/>
       <c r="C281" s="2"/>
       <c r="I281"/>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A282" s="13" t="s">
-        <v>138</v>
-      </c>
+      <c r="A282" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="B282" s="4"/>
       <c r="C282" s="2"/>
       <c r="I282"/>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A283" s="13" t="s">
-        <v>139</v>
-      </c>
+      <c r="A283" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="B283" s="4"/>
       <c r="C283" s="2"/>
       <c r="I283"/>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A284" s="13" t="s">
+      <c r="A284" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B284" s="4"/>
+      <c r="C284" s="2"/>
+      <c r="I284"/>
+    </row>
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A285" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="B285" s="4"/>
+      <c r="C285" s="2"/>
+      <c r="I285"/>
+    </row>
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A286" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="B286" s="4"/>
+      <c r="C286" s="2"/>
+      <c r="I286"/>
+    </row>
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A287" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="B287" s="4"/>
+      <c r="C287" s="2"/>
+      <c r="I287"/>
+    </row>
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A288" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C288" s="2"/>
+      <c r="I288"/>
+    </row>
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A289" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C289" s="2"/>
+      <c r="I289"/>
+    </row>
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A290" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="C290" s="2"/>
+      <c r="I290"/>
+    </row>
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A291" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C291" s="2"/>
+      <c r="I291"/>
+    </row>
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A292" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C292" s="2"/>
+      <c r="I292"/>
+    </row>
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A293" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="C293" s="2"/>
+      <c r="I293"/>
+    </row>
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A294" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C294" s="2"/>
+      <c r="I294"/>
+    </row>
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A295" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="C295" s="2"/>
+      <c r="I295"/>
+    </row>
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A296" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C296" s="2"/>
+      <c r="I296"/>
+    </row>
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A297" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C297" s="2"/>
+      <c r="I297"/>
+    </row>
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A298" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C298" s="2"/>
+      <c r="I298"/>
+    </row>
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A299" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C299" s="2"/>
+      <c r="I299"/>
+    </row>
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A300" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C300" s="2"/>
+      <c r="I300"/>
+    </row>
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A301" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="C301" s="2"/>
+      <c r="I301"/>
+    </row>
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A302" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C302" s="2"/>
+      <c r="I302"/>
+    </row>
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A303" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="C303" s="2"/>
+      <c r="I303"/>
+    </row>
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A304" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C304" s="2"/>
+      <c r="I304"/>
+    </row>
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A305" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="C305" s="2"/>
+      <c r="I305"/>
+    </row>
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A306" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C306" s="2"/>
+      <c r="I306"/>
+    </row>
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A307" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="C307" s="2"/>
+      <c r="I307"/>
+    </row>
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A308" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="C308" s="2"/>
+      <c r="I308"/>
+    </row>
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A309" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C309" s="2"/>
+      <c r="I309"/>
+    </row>
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A310" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="C310" s="2"/>
+      <c r="I310"/>
+    </row>
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A311" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="C311" s="2"/>
+      <c r="I311"/>
+    </row>
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A312" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="C312" s="2"/>
+      <c r="I312"/>
+    </row>
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A313" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="C313" s="2"/>
+      <c r="I313"/>
+    </row>
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A314" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="C314" s="2"/>
+      <c r="I314"/>
+    </row>
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A315" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="C315" s="2"/>
+      <c r="I315"/>
+    </row>
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A316" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="C316" s="2"/>
+      <c r="I316"/>
+    </row>
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A317" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="C317" s="2"/>
+      <c r="I317"/>
+    </row>
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A318" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="C318" s="2"/>
+      <c r="I318"/>
+    </row>
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A319" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="C319" s="2"/>
+      <c r="I319"/>
+    </row>
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A320" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B284" s="2">
+      <c r="B320" s="2">
         <v>11500</v>
       </c>
-      <c r="C284" s="2">
+      <c r="C320" s="2">
         <v>1300</v>
       </c>
-      <c r="I284"/>
-    </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A285" s="13" t="s">
+      <c r="I320"/>
+    </row>
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A321" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="B285" s="2">
+      <c r="B321" s="2">
         <v>11500</v>
       </c>
-      <c r="C285" s="2">
+      <c r="C321" s="2">
         <v>1300</v>
       </c>
-      <c r="I285"/>
-    </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A286" s="13" t="s">
+      <c r="I321"/>
+    </row>
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A322" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="B286" s="2">
+      <c r="B322" s="2">
         <v>11500</v>
       </c>
-      <c r="C286" s="2">
+      <c r="C322" s="2">
         <v>1300</v>
       </c>
-      <c r="I286"/>
-    </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A287" s="13" t="s">
+      <c r="I322"/>
+    </row>
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A323" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="B287" s="2">
+      <c r="B323" s="2">
         <v>11500</v>
       </c>
-      <c r="C287" s="2">
+      <c r="C323" s="2">
         <v>1300</v>
       </c>
-      <c r="I287"/>
-    </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A288" s="13" t="s">
+      <c r="I323"/>
+    </row>
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A324" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="B288" s="2">
+      <c r="B324" s="2">
         <v>11500</v>
       </c>
-      <c r="C288" s="2">
+      <c r="C324" s="2">
         <v>1300</v>
       </c>
-      <c r="I288"/>
-    </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A289" s="13" t="s">
+      <c r="I324"/>
+    </row>
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A325" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="B289" s="2">
+      <c r="B325" s="2">
         <v>11500</v>
       </c>
-      <c r="C289" s="2">
+      <c r="C325" s="2">
         <v>1300</v>
       </c>
-      <c r="I289"/>
-    </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A290" s="13" t="s">
+      <c r="I325"/>
+    </row>
+    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A326" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="B290" s="2">
+      <c r="B326" s="2">
         <v>11500</v>
       </c>
-      <c r="C290" s="2">
+      <c r="C326" s="2">
         <v>1300</v>
       </c>
-      <c r="I290"/>
-    </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A291" s="13" t="s">
+      <c r="I326"/>
+    </row>
+    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A327" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="B291" s="2">
+      <c r="B327" s="2">
         <v>11500</v>
       </c>
-      <c r="C291" s="2">
+      <c r="C327" s="2">
         <v>1300</v>
       </c>
-      <c r="I291"/>
-    </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A292" s="13" t="s">
+      <c r="I327"/>
+    </row>
+    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A328" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="B292" s="2">
+      <c r="B328" s="2">
         <v>11500</v>
       </c>
-      <c r="C292" s="2">
+      <c r="C328" s="2">
         <v>1300</v>
       </c>
-      <c r="I292"/>
-    </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A293" s="13" t="s">
+      <c r="I328"/>
+    </row>
+    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A329" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="B293" s="2">
+      <c r="B329" s="2">
         <v>11500</v>
       </c>
-      <c r="C293" s="2">
+      <c r="C329" s="2">
         <v>1300</v>
       </c>
-      <c r="I293"/>
-    </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A294" s="13" t="s">
+      <c r="I329"/>
+    </row>
+    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A330" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="B294" s="2">
+      <c r="B330" s="2">
         <v>11500</v>
       </c>
-      <c r="C294" s="2">
+      <c r="C330" s="2">
         <v>1300</v>
       </c>
-      <c r="I294"/>
-    </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A295" s="13" t="s">
+      <c r="I330"/>
+    </row>
+    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A331" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="B295" s="2">
+      <c r="B331" s="2">
         <v>11500</v>
       </c>
-      <c r="C295" s="2">
+      <c r="C331" s="2">
         <v>1300</v>
       </c>
-      <c r="I295"/>
-    </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A296" s="13" t="s">
+      <c r="I331"/>
+    </row>
+    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A332" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="B296" s="2">
+      <c r="B332" s="2">
         <v>11500</v>
       </c>
-      <c r="C296" s="2">
+      <c r="C332" s="2">
         <v>1300</v>
       </c>
-      <c r="I296"/>
-    </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A297" s="13" t="s">
+      <c r="I332"/>
+    </row>
+    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A333" s="12" t="s">
         <v>623</v>
       </c>
-      <c r="B297" s="2">
+      <c r="B333" s="2">
         <v>11500</v>
       </c>
-      <c r="C297" s="2">
+      <c r="C333" s="2">
         <v>1300</v>
       </c>
-      <c r="I297"/>
-    </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A298" s="13" t="s">
+      <c r="I333"/>
+    </row>
+    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A334" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="B298" s="2">
+      <c r="B334" s="2">
         <v>11500</v>
       </c>
-      <c r="C298" s="2">
+      <c r="C334" s="2">
         <v>1300</v>
       </c>
-      <c r="I298"/>
-    </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A299" s="13" t="s">
+      <c r="I334"/>
+    </row>
+    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A335" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="B299" s="2">
+      <c r="B335" s="2">
         <v>11500</v>
       </c>
-      <c r="C299" s="2">
+      <c r="C335" s="2">
         <v>1300</v>
       </c>
-      <c r="I299"/>
-    </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A300" s="13" t="s">
+      <c r="I335"/>
+    </row>
+    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A336" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="B300" s="2">
+      <c r="B336" s="2">
         <v>11500</v>
       </c>
-      <c r="C300" s="2">
+      <c r="C336" s="2">
         <v>1300</v>
       </c>
-      <c r="I300"/>
-    </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A301" s="13" t="s">
+      <c r="I336"/>
+    </row>
+    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A337" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="B301" s="2">
+      <c r="B337" s="2">
         <v>11500</v>
       </c>
-      <c r="C301" s="2">
+      <c r="C337" s="2">
         <v>1300</v>
       </c>
-      <c r="I301"/>
-    </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A302" s="13" t="s">
+      <c r="I337"/>
+    </row>
+    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A338" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="B302" s="2">
+      <c r="B338" s="2">
         <v>11500</v>
       </c>
-      <c r="C302" s="2">
+      <c r="C338" s="2">
         <v>1300</v>
       </c>
-      <c r="I302"/>
-    </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A303" s="13" t="s">
+      <c r="I338"/>
+    </row>
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A339" s="12" t="s">
         <v>624</v>
       </c>
-      <c r="B303" s="2">
+      <c r="B339" s="2">
         <v>11500</v>
       </c>
-      <c r="C303" s="2">
+      <c r="C339" s="2">
         <v>1300</v>
       </c>
-      <c r="I303"/>
-    </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A304" s="13" t="s">
+      <c r="I339"/>
+    </row>
+    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A340" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="B304" s="2">
+      <c r="B340" s="2">
         <v>11500</v>
       </c>
-      <c r="C304" s="2">
+      <c r="C340" s="2">
         <v>1300</v>
       </c>
-      <c r="I304"/>
-    </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A305" s="13" t="s">
+      <c r="I340"/>
+    </row>
+    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A341" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="B305" s="2">
+      <c r="B341" s="2">
         <v>11500</v>
       </c>
-      <c r="C305" s="2">
+      <c r="C341" s="2">
         <v>1300</v>
       </c>
-      <c r="I305"/>
-    </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A306" s="13" t="s">
+      <c r="I341"/>
+    </row>
+    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A342" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="B306" s="2">
+      <c r="B342" s="2">
         <v>11500</v>
       </c>
-      <c r="C306" s="2">
+      <c r="C342" s="2">
         <v>1300</v>
       </c>
-      <c r="I306"/>
-    </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A307" s="13" t="s">
+      <c r="I342"/>
+    </row>
+    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A343" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="B307" s="2">
+      <c r="B343" s="2">
         <v>11500</v>
       </c>
-      <c r="C307" s="2">
+      <c r="C343" s="2">
         <v>1300</v>
       </c>
-      <c r="I307"/>
-    </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A308" s="13" t="s">
+      <c r="I343"/>
+    </row>
+    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A344" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="B308" s="2">
+      <c r="B344" s="2">
         <v>11500</v>
       </c>
-      <c r="C308" s="2">
+      <c r="C344" s="2">
         <v>1300</v>
       </c>
-      <c r="I308"/>
-    </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A309" s="13" t="s">
+      <c r="I344"/>
+    </row>
+    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A345" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="B309" s="2">
+      <c r="B345" s="2">
         <v>11500</v>
       </c>
-      <c r="C309" s="2">
+      <c r="C345" s="2">
         <v>1300</v>
       </c>
-      <c r="I309"/>
-    </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A310" s="13" t="s">
+      <c r="I345"/>
+    </row>
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A346" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="B310" s="2">
+      <c r="B346" s="2">
         <v>11500</v>
       </c>
-      <c r="C310" s="2">
+      <c r="C346" s="2">
         <v>1300</v>
       </c>
-      <c r="I310"/>
-    </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A311" s="13" t="s">
+      <c r="I346"/>
+    </row>
+    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A347" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="B311" s="2">
+      <c r="B347" s="2">
         <v>11500</v>
       </c>
-      <c r="C311" s="2">
+      <c r="C347" s="2">
         <v>1300</v>
       </c>
-      <c r="I311"/>
-    </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A312" s="13" t="s">
+      <c r="I347"/>
+    </row>
+    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A348" s="12" t="s">
         <v>488</v>
       </c>
-      <c r="B312" s="2">
+      <c r="B348" s="2">
         <v>11500</v>
       </c>
-      <c r="C312" s="2">
+      <c r="C348" s="2">
         <v>1300</v>
       </c>
-      <c r="I312"/>
-    </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A313" s="13" t="s">
+      <c r="I348"/>
+    </row>
+    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A349" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="B313" s="2">
+      <c r="B349" s="2">
         <v>11500</v>
       </c>
-      <c r="C313" s="2">
+      <c r="C349" s="2">
         <v>1300</v>
       </c>
-      <c r="I313"/>
-    </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A314" s="13" t="s">
+      <c r="I349"/>
+    </row>
+    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A350" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="B314" s="2">
+      <c r="B350" s="2">
         <v>11500</v>
       </c>
-      <c r="C314" s="2">
+      <c r="C350" s="2">
         <v>1300</v>
       </c>
-      <c r="I314"/>
-    </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A315" s="13" t="s">
+      <c r="I350"/>
+    </row>
+    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A351" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="B315" s="2">
+      <c r="B351" s="2">
         <v>11500</v>
       </c>
-      <c r="C315" s="2">
+      <c r="C351" s="2">
         <v>1300</v>
       </c>
-      <c r="I315"/>
-    </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A316" s="13" t="s">
+      <c r="I351"/>
+    </row>
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A352" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="B316" s="2">
+      <c r="B352" s="2">
         <v>11500</v>
       </c>
-      <c r="C316" s="2">
+      <c r="C352" s="2">
         <v>1300</v>
       </c>
-      <c r="I316"/>
-    </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A317" s="13" t="s">
+      <c r="I352"/>
+    </row>
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A353" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="B317" s="2">
+      <c r="B353" s="2">
         <v>11500</v>
       </c>
-      <c r="C317" s="2">
+      <c r="C353" s="2">
         <v>1300</v>
       </c>
-      <c r="I317"/>
-    </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A318" s="13" t="s">
+      <c r="I353"/>
+    </row>
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A354" s="12" t="s">
         <v>171</v>
-      </c>
-      <c r="B318" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C318" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I318"/>
-    </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A319" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="B319" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C319" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I319"/>
-    </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A320" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="B320" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C320" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I320"/>
-    </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A321" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="B321" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C321" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I321"/>
-    </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A322" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="B322" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C322" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I322"/>
-    </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A323" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="B323" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C323" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I323"/>
-    </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A324" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="B324" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C324" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I324"/>
-    </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A325" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="B325" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C325" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I325"/>
-    </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A326" s="13" t="s">
-        <v>625</v>
-      </c>
-      <c r="B326" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C326" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I326"/>
-    </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A327" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="B327" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C327" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I327"/>
-    </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A328" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="B328" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C328" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I328"/>
-    </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A329" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="B329" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C329" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I329"/>
-    </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A330" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="B330" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C330" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I330"/>
-    </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A331" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="B331" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C331" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I331"/>
-    </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A332" s="13" t="s">
-        <v>626</v>
-      </c>
-      <c r="B332" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C332" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I332"/>
-    </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A333" s="13" t="s">
-        <v>444</v>
-      </c>
-      <c r="B333" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C333" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I333"/>
-    </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A334" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="B334" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C334" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I334"/>
-    </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A335" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="B335" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C335" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I335"/>
-    </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A336" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="B336" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C336" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I336"/>
-    </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A337" s="13" t="s">
-        <v>627</v>
-      </c>
-      <c r="B337" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C337" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I337"/>
-    </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A338" s="13" t="s">
-        <v>628</v>
-      </c>
-      <c r="B338" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C338" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I338"/>
-    </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A339" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="B339" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C339" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I339"/>
-    </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A340" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="B340" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C340" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I340"/>
-    </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A341" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="B341" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C341" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I341"/>
-    </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A342" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="B342" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C342" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I342"/>
-    </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A343" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="B343" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C343" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I343"/>
-    </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A344" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="B344" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C344" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I344"/>
-    </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A345" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="B345" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C345" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I345"/>
-    </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A346" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="B346" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C346" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I346"/>
-    </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A347" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="B347" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C347" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I347"/>
-    </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A348" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="B348" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C348" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I348"/>
-    </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A349" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="B349" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C349" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I349"/>
-    </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A350" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="B350" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C350" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I350"/>
-    </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A351" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="B351" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C351" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I351"/>
-    </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A352" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="B352" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C352" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I352"/>
-    </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A353" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="B353" s="2">
-        <v>9000</v>
-      </c>
-      <c r="C353" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I353"/>
-    </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A354" s="13" t="s">
-        <v>202</v>
       </c>
       <c r="B354" s="2">
         <v>9000</v>
@@ -6495,8 +6634,8 @@
       <c r="I354"/>
     </row>
     <row r="355" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A355" s="13" t="s">
-        <v>203</v>
+      <c r="A355" s="12" t="s">
+        <v>172</v>
       </c>
       <c r="B355" s="2">
         <v>9000</v>
@@ -6507,440 +6646,440 @@
       <c r="I355"/>
     </row>
     <row r="356" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A356" s="13" t="s">
+      <c r="A356" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="B356" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C356" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I356"/>
+    </row>
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A357" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="B357" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C357" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I357"/>
+    </row>
+    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A358" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="B358" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C358" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I358"/>
+    </row>
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A359" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="B359" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C359" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I359"/>
+    </row>
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A360" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="B360" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C360" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I360"/>
+    </row>
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A361" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="B361" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C361" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I361"/>
+    </row>
+    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A362" s="12" t="s">
+        <v>625</v>
+      </c>
+      <c r="B362" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C362" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I362"/>
+    </row>
+    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A363" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="B363" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C363" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I363"/>
+    </row>
+    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A364" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B364" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C364" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I364"/>
+    </row>
+    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A365" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="B365" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C365" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I365"/>
+    </row>
+    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A366" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="B366" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C366" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I366"/>
+    </row>
+    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A367" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="B367" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C367" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I367"/>
+    </row>
+    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A368" s="12" t="s">
+        <v>626</v>
+      </c>
+      <c r="B368" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C368" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I368"/>
+    </row>
+    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A369" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="B369" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C369" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I369"/>
+    </row>
+    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A370" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="B370" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C370" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I370"/>
+    </row>
+    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A371" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="B371" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C371" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I371"/>
+    </row>
+    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A372" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="B372" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C372" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I372"/>
+    </row>
+    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A373" s="12" t="s">
+        <v>627</v>
+      </c>
+      <c r="B373" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C373" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I373"/>
+    </row>
+    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A374" s="12" t="s">
+        <v>628</v>
+      </c>
+      <c r="B374" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C374" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I374"/>
+    </row>
+    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A375" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="B375" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C375" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I375"/>
+    </row>
+    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A376" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="B376" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C376" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I376"/>
+    </row>
+    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A377" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="B377" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C377" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I377"/>
+    </row>
+    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A378" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="B378" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C378" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I378"/>
+    </row>
+    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A379" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="B379" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C379" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I379"/>
+    </row>
+    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A380" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="B380" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C380" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I380"/>
+    </row>
+    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A381" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="B381" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C381" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I381"/>
+    </row>
+    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A382" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="B382" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C382" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I382"/>
+    </row>
+    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A383" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="B383" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C383" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I383"/>
+    </row>
+    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A384" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="B384" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C384" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I384"/>
+    </row>
+    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A385" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="B385" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C385" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I385"/>
+    </row>
+    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A386" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="B386" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C386" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I386"/>
+    </row>
+    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A387" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="B387" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C387" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I387"/>
+    </row>
+    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A388" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="B388" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C388" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I388"/>
+    </row>
+    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A389" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="B389" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C389" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I389"/>
+    </row>
+    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A390" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="B390" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C390" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I390"/>
+    </row>
+    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A391" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="B391" s="2">
+        <v>9000</v>
+      </c>
+      <c r="C391" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I391"/>
+    </row>
+    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A392" s="12" t="s">
         <v>204</v>
-      </c>
-      <c r="B356" s="4">
-        <v>10000</v>
-      </c>
-      <c r="C356" s="2">
-        <v>1800</v>
-      </c>
-      <c r="I356"/>
-    </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A357" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="B357" s="4">
-        <v>8000</v>
-      </c>
-      <c r="C357" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I357"/>
-    </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A358" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="B358" s="4">
-        <v>12000</v>
-      </c>
-      <c r="C358" s="2">
-        <v>2000</v>
-      </c>
-      <c r="I358"/>
-    </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A359" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="B359" s="4">
-        <v>10000</v>
-      </c>
-      <c r="C359" s="2">
-        <v>1800</v>
-      </c>
-      <c r="I359"/>
-    </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A360" s="13" t="s">
-        <v>208</v>
-      </c>
-      <c r="B360" s="4">
-        <v>8000</v>
-      </c>
-      <c r="C360" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I360"/>
-    </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A361" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="B361" s="4">
-        <v>12000</v>
-      </c>
-      <c r="C361" s="2">
-        <v>2000</v>
-      </c>
-      <c r="I361"/>
-    </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A362" s="13" t="s">
-        <v>210</v>
-      </c>
-      <c r="B362" s="4">
-        <v>10000</v>
-      </c>
-      <c r="C362" s="2">
-        <v>1800</v>
-      </c>
-      <c r="I362"/>
-    </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A363" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="B363" s="4">
-        <v>8000</v>
-      </c>
-      <c r="C363" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I363"/>
-    </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A364" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="B364" s="4">
-        <v>12000</v>
-      </c>
-      <c r="C364" s="2">
-        <v>2000</v>
-      </c>
-      <c r="I364"/>
-    </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A365" s="13" t="s">
-        <v>213</v>
-      </c>
-      <c r="B365" s="4">
-        <v>10000</v>
-      </c>
-      <c r="C365" s="2">
-        <v>1800</v>
-      </c>
-      <c r="I365"/>
-    </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A366" s="13" t="s">
-        <v>214</v>
-      </c>
-      <c r="B366" s="4">
-        <v>8000</v>
-      </c>
-      <c r="C366" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I366"/>
-    </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A367" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="B367" s="4">
-        <v>12000</v>
-      </c>
-      <c r="C367" s="2">
-        <v>2000</v>
-      </c>
-      <c r="I367"/>
-    </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A368" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="B368" s="4">
-        <v>10000</v>
-      </c>
-      <c r="C368" s="2">
-        <v>1800</v>
-      </c>
-      <c r="I368"/>
-    </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A369" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="B369" s="4">
-        <v>8000</v>
-      </c>
-      <c r="C369" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I369"/>
-    </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A370" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="B370" s="4">
-        <v>12000</v>
-      </c>
-      <c r="C370" s="2">
-        <v>2000</v>
-      </c>
-      <c r="I370"/>
-    </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A371" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="B371" s="4">
-        <v>10000</v>
-      </c>
-      <c r="C371" s="2">
-        <v>1800</v>
-      </c>
-      <c r="I371"/>
-    </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A372" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="B372" s="4">
-        <v>8000</v>
-      </c>
-      <c r="C372" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I372"/>
-    </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A373" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="B373" s="4">
-        <v>12000</v>
-      </c>
-      <c r="C373" s="2">
-        <v>2000</v>
-      </c>
-      <c r="I373"/>
-    </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A374" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="B374" s="4">
-        <v>10000</v>
-      </c>
-      <c r="C374" s="2">
-        <v>1800</v>
-      </c>
-      <c r="I374"/>
-    </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A375" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="B375" s="4">
-        <v>8000</v>
-      </c>
-      <c r="C375" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I375"/>
-    </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A376" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="B376" s="4">
-        <v>12000</v>
-      </c>
-      <c r="C376" s="2">
-        <v>2000</v>
-      </c>
-      <c r="I376"/>
-    </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A377" s="13" t="s">
-        <v>225</v>
-      </c>
-      <c r="B377" s="4">
-        <v>10000</v>
-      </c>
-      <c r="C377" s="2">
-        <v>1800</v>
-      </c>
-      <c r="I377"/>
-    </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A378" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="B378" s="4">
-        <v>8000</v>
-      </c>
-      <c r="C378" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I378"/>
-    </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A379" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="B379" s="4">
-        <v>12000</v>
-      </c>
-      <c r="C379" s="2">
-        <v>2000</v>
-      </c>
-      <c r="I379"/>
-    </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A380" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="B380" s="4">
-        <v>10000</v>
-      </c>
-      <c r="C380" s="2">
-        <v>1800</v>
-      </c>
-      <c r="I380"/>
-    </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A381" s="13" t="s">
-        <v>229</v>
-      </c>
-      <c r="B381" s="4">
-        <v>8000</v>
-      </c>
-      <c r="C381" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I381"/>
-    </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A382" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="B382" s="4">
-        <v>12000</v>
-      </c>
-      <c r="C382" s="2">
-        <v>2000</v>
-      </c>
-      <c r="I382"/>
-    </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A383" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="B383" s="4">
-        <v>10000</v>
-      </c>
-      <c r="C383" s="2">
-        <v>1800</v>
-      </c>
-      <c r="I383"/>
-    </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A384" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="B384" s="4">
-        <v>8000</v>
-      </c>
-      <c r="C384" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I384"/>
-    </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A385" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="B385" s="4">
-        <v>12000</v>
-      </c>
-      <c r="C385" s="2">
-        <v>2000</v>
-      </c>
-      <c r="I385"/>
-    </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A386" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="B386" s="4">
-        <v>10000</v>
-      </c>
-      <c r="C386" s="2">
-        <v>1800</v>
-      </c>
-      <c r="I386"/>
-    </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A387" s="13" t="s">
-        <v>235</v>
-      </c>
-      <c r="B387" s="4">
-        <v>8000</v>
-      </c>
-      <c r="C387" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I387"/>
-    </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A388" s="13" t="s">
-        <v>236</v>
-      </c>
-      <c r="B388" s="4">
-        <v>12000</v>
-      </c>
-      <c r="C388" s="2">
-        <v>2000</v>
-      </c>
-      <c r="I388"/>
-    </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A389" s="13" t="s">
-        <v>237</v>
-      </c>
-      <c r="B389" s="4">
-        <v>10000</v>
-      </c>
-      <c r="C389" s="2">
-        <v>1800</v>
-      </c>
-      <c r="I389"/>
-    </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A390" s="13" t="s">
-        <v>238</v>
-      </c>
-      <c r="B390" s="4">
-        <v>8000</v>
-      </c>
-      <c r="C390" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I390"/>
-    </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A391" s="13" t="s">
-        <v>239</v>
-      </c>
-      <c r="B391" s="4">
-        <v>12000</v>
-      </c>
-      <c r="C391" s="2">
-        <v>2000</v>
-      </c>
-      <c r="I391"/>
-    </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A392" s="13" t="s">
-        <v>240</v>
       </c>
       <c r="B392" s="4">
         <v>10000</v>
@@ -6951,8 +7090,8 @@
       <c r="I392"/>
     </row>
     <row r="393" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A393" s="13" t="s">
-        <v>241</v>
+      <c r="A393" s="12" t="s">
+        <v>205</v>
       </c>
       <c r="B393" s="4">
         <v>8000</v>
@@ -6963,8 +7102,8 @@
       <c r="I393"/>
     </row>
     <row r="394" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A394" s="13" t="s">
-        <v>242</v>
+      <c r="A394" s="12" t="s">
+        <v>206</v>
       </c>
       <c r="B394" s="4">
         <v>12000</v>
@@ -6975,8 +7114,8 @@
       <c r="I394"/>
     </row>
     <row r="395" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A395" s="13" t="s">
-        <v>629</v>
+      <c r="A395" s="12" t="s">
+        <v>207</v>
       </c>
       <c r="B395" s="4">
         <v>10000</v>
@@ -6987,8 +7126,8 @@
       <c r="I395"/>
     </row>
     <row r="396" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A396" s="13" t="s">
-        <v>630</v>
+      <c r="A396" s="12" t="s">
+        <v>208</v>
       </c>
       <c r="B396" s="4">
         <v>8000</v>
@@ -6999,8 +7138,8 @@
       <c r="I396"/>
     </row>
     <row r="397" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A397" s="13" t="s">
-        <v>631</v>
+      <c r="A397" s="12" t="s">
+        <v>209</v>
       </c>
       <c r="B397" s="4">
         <v>12000</v>
@@ -7011,8 +7150,8 @@
       <c r="I397"/>
     </row>
     <row r="398" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A398" s="13" t="s">
-        <v>243</v>
+      <c r="A398" s="12" t="s">
+        <v>210</v>
       </c>
       <c r="B398" s="4">
         <v>10000</v>
@@ -7023,8 +7162,8 @@
       <c r="I398"/>
     </row>
     <row r="399" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A399" s="13" t="s">
-        <v>244</v>
+      <c r="A399" s="12" t="s">
+        <v>211</v>
       </c>
       <c r="B399" s="4">
         <v>8000</v>
@@ -7035,8 +7174,8 @@
       <c r="I399"/>
     </row>
     <row r="400" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A400" s="13" t="s">
-        <v>245</v>
+      <c r="A400" s="12" t="s">
+        <v>212</v>
       </c>
       <c r="B400" s="4">
         <v>12000</v>
@@ -7047,8 +7186,8 @@
       <c r="I400"/>
     </row>
     <row r="401" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A401" s="13" t="s">
-        <v>246</v>
+      <c r="A401" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="B401" s="4">
         <v>10000</v>
@@ -7059,8 +7198,8 @@
       <c r="I401"/>
     </row>
     <row r="402" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A402" s="13" t="s">
-        <v>247</v>
+      <c r="A402" s="12" t="s">
+        <v>214</v>
       </c>
       <c r="B402" s="4">
         <v>8000</v>
@@ -7071,8 +7210,8 @@
       <c r="I402"/>
     </row>
     <row r="403" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A403" s="13" t="s">
-        <v>248</v>
+      <c r="A403" s="12" t="s">
+        <v>215</v>
       </c>
       <c r="B403" s="4">
         <v>12000</v>
@@ -7083,8 +7222,8 @@
       <c r="I403"/>
     </row>
     <row r="404" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A404" s="13" t="s">
-        <v>249</v>
+      <c r="A404" s="12" t="s">
+        <v>216</v>
       </c>
       <c r="B404" s="4">
         <v>10000</v>
@@ -7095,8 +7234,8 @@
       <c r="I404"/>
     </row>
     <row r="405" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A405" s="13" t="s">
-        <v>250</v>
+      <c r="A405" s="12" t="s">
+        <v>217</v>
       </c>
       <c r="B405" s="4">
         <v>8000</v>
@@ -7107,8 +7246,8 @@
       <c r="I405"/>
     </row>
     <row r="406" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A406" s="13" t="s">
-        <v>251</v>
+      <c r="A406" s="12" t="s">
+        <v>218</v>
       </c>
       <c r="B406" s="4">
         <v>12000</v>
@@ -7119,8 +7258,8 @@
       <c r="I406"/>
     </row>
     <row r="407" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A407" s="13" t="s">
-        <v>252</v>
+      <c r="A407" s="12" t="s">
+        <v>219</v>
       </c>
       <c r="B407" s="4">
         <v>10000</v>
@@ -7131,8 +7270,8 @@
       <c r="I407"/>
     </row>
     <row r="408" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A408" s="13" t="s">
-        <v>253</v>
+      <c r="A408" s="12" t="s">
+        <v>220</v>
       </c>
       <c r="B408" s="4">
         <v>8000</v>
@@ -7143,8 +7282,8 @@
       <c r="I408"/>
     </row>
     <row r="409" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A409" s="13" t="s">
-        <v>254</v>
+      <c r="A409" s="12" t="s">
+        <v>221</v>
       </c>
       <c r="B409" s="4">
         <v>12000</v>
@@ -7155,8 +7294,8 @@
       <c r="I409"/>
     </row>
     <row r="410" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A410" s="13" t="s">
-        <v>255</v>
+      <c r="A410" s="12" t="s">
+        <v>222</v>
       </c>
       <c r="B410" s="4">
         <v>10000</v>
@@ -7167,8 +7306,8 @@
       <c r="I410"/>
     </row>
     <row r="411" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A411" s="13" t="s">
-        <v>256</v>
+      <c r="A411" s="12" t="s">
+        <v>223</v>
       </c>
       <c r="B411" s="4">
         <v>8000</v>
@@ -7179,8 +7318,8 @@
       <c r="I411"/>
     </row>
     <row r="412" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A412" s="13" t="s">
-        <v>257</v>
+      <c r="A412" s="12" t="s">
+        <v>224</v>
       </c>
       <c r="B412" s="4">
         <v>12000</v>
@@ -7191,8 +7330,8 @@
       <c r="I412"/>
     </row>
     <row r="413" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A413" s="13" t="s">
-        <v>258</v>
+      <c r="A413" s="12" t="s">
+        <v>225</v>
       </c>
       <c r="B413" s="4">
         <v>10000</v>
@@ -7203,8 +7342,8 @@
       <c r="I413"/>
     </row>
     <row r="414" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A414" s="13" t="s">
-        <v>259</v>
+      <c r="A414" s="12" t="s">
+        <v>226</v>
       </c>
       <c r="B414" s="4">
         <v>8000</v>
@@ -7215,8 +7354,8 @@
       <c r="I414"/>
     </row>
     <row r="415" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A415" s="13" t="s">
-        <v>260</v>
+      <c r="A415" s="12" t="s">
+        <v>227</v>
       </c>
       <c r="B415" s="4">
         <v>12000</v>
@@ -7227,8 +7366,8 @@
       <c r="I415"/>
     </row>
     <row r="416" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A416" s="13" t="s">
-        <v>261</v>
+      <c r="A416" s="12" t="s">
+        <v>228</v>
       </c>
       <c r="B416" s="4">
         <v>10000</v>
@@ -7239,8 +7378,8 @@
       <c r="I416"/>
     </row>
     <row r="417" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A417" s="13" t="s">
-        <v>262</v>
+      <c r="A417" s="12" t="s">
+        <v>229</v>
       </c>
       <c r="B417" s="4">
         <v>8000</v>
@@ -7251,8 +7390,8 @@
       <c r="I417"/>
     </row>
     <row r="418" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A418" s="13" t="s">
-        <v>263</v>
+      <c r="A418" s="12" t="s">
+        <v>230</v>
       </c>
       <c r="B418" s="4">
         <v>12000</v>
@@ -7263,8 +7402,8 @@
       <c r="I418"/>
     </row>
     <row r="419" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A419" s="13" t="s">
-        <v>264</v>
+      <c r="A419" s="12" t="s">
+        <v>231</v>
       </c>
       <c r="B419" s="4">
         <v>10000</v>
@@ -7275,8 +7414,8 @@
       <c r="I419"/>
     </row>
     <row r="420" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A420" s="13" t="s">
-        <v>265</v>
+      <c r="A420" s="12" t="s">
+        <v>232</v>
       </c>
       <c r="B420" s="4">
         <v>8000</v>
@@ -7287,8 +7426,8 @@
       <c r="I420"/>
     </row>
     <row r="421" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A421" s="13" t="s">
-        <v>266</v>
+      <c r="A421" s="12" t="s">
+        <v>233</v>
       </c>
       <c r="B421" s="4">
         <v>12000</v>
@@ -7299,8 +7438,8 @@
       <c r="I421"/>
     </row>
     <row r="422" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A422" s="13" t="s">
-        <v>267</v>
+      <c r="A422" s="12" t="s">
+        <v>234</v>
       </c>
       <c r="B422" s="4">
         <v>10000</v>
@@ -7311,8 +7450,8 @@
       <c r="I422"/>
     </row>
     <row r="423" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A423" s="13" t="s">
-        <v>268</v>
+      <c r="A423" s="12" t="s">
+        <v>235</v>
       </c>
       <c r="B423" s="4">
         <v>8000</v>
@@ -7323,8 +7462,8 @@
       <c r="I423"/>
     </row>
     <row r="424" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A424" s="13" t="s">
-        <v>269</v>
+      <c r="A424" s="12" t="s">
+        <v>236</v>
       </c>
       <c r="B424" s="4">
         <v>12000</v>
@@ -7335,8 +7474,8 @@
       <c r="I424"/>
     </row>
     <row r="425" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A425" s="13" t="s">
-        <v>270</v>
+      <c r="A425" s="12" t="s">
+        <v>237</v>
       </c>
       <c r="B425" s="4">
         <v>10000</v>
@@ -7347,8 +7486,8 @@
       <c r="I425"/>
     </row>
     <row r="426" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A426" s="13" t="s">
-        <v>271</v>
+      <c r="A426" s="12" t="s">
+        <v>238</v>
       </c>
       <c r="B426" s="4">
         <v>8000</v>
@@ -7359,8 +7498,8 @@
       <c r="I426"/>
     </row>
     <row r="427" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A427" s="13" t="s">
-        <v>272</v>
+      <c r="A427" s="12" t="s">
+        <v>239</v>
       </c>
       <c r="B427" s="4">
         <v>12000</v>
@@ -7371,8 +7510,8 @@
       <c r="I427"/>
     </row>
     <row r="428" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A428" s="13" t="s">
-        <v>273</v>
+      <c r="A428" s="12" t="s">
+        <v>240</v>
       </c>
       <c r="B428" s="4">
         <v>10000</v>
@@ -7383,8 +7522,8 @@
       <c r="I428"/>
     </row>
     <row r="429" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A429" s="13" t="s">
-        <v>274</v>
+      <c r="A429" s="12" t="s">
+        <v>241</v>
       </c>
       <c r="B429" s="4">
         <v>8000</v>
@@ -7395,8 +7534,8 @@
       <c r="I429"/>
     </row>
     <row r="430" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A430" s="13" t="s">
-        <v>275</v>
+      <c r="A430" s="12" t="s">
+        <v>242</v>
       </c>
       <c r="B430" s="4">
         <v>12000</v>
@@ -7407,8 +7546,8 @@
       <c r="I430"/>
     </row>
     <row r="431" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A431" s="13" t="s">
-        <v>276</v>
+      <c r="A431" s="12" t="s">
+        <v>629</v>
       </c>
       <c r="B431" s="4">
         <v>10000</v>
@@ -7419,8 +7558,8 @@
       <c r="I431"/>
     </row>
     <row r="432" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A432" s="13" t="s">
-        <v>277</v>
+      <c r="A432" s="12" t="s">
+        <v>630</v>
       </c>
       <c r="B432" s="4">
         <v>8000</v>
@@ -7431,8 +7570,8 @@
       <c r="I432"/>
     </row>
     <row r="433" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A433" s="13" t="s">
-        <v>278</v>
+      <c r="A433" s="12" t="s">
+        <v>631</v>
       </c>
       <c r="B433" s="4">
         <v>12000</v>
@@ -7443,8 +7582,8 @@
       <c r="I433"/>
     </row>
     <row r="434" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A434" s="13" t="s">
-        <v>279</v>
+      <c r="A434" s="12" t="s">
+        <v>243</v>
       </c>
       <c r="B434" s="4">
         <v>10000</v>
@@ -7455,8 +7594,8 @@
       <c r="I434"/>
     </row>
     <row r="435" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A435" s="13" t="s">
-        <v>280</v>
+      <c r="A435" s="12" t="s">
+        <v>244</v>
       </c>
       <c r="B435" s="4">
         <v>8000</v>
@@ -7467,8 +7606,8 @@
       <c r="I435"/>
     </row>
     <row r="436" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A436" s="13" t="s">
-        <v>281</v>
+      <c r="A436" s="12" t="s">
+        <v>245</v>
       </c>
       <c r="B436" s="4">
         <v>12000</v>
@@ -7479,8 +7618,8 @@
       <c r="I436"/>
     </row>
     <row r="437" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A437" s="13" t="s">
-        <v>282</v>
+      <c r="A437" s="12" t="s">
+        <v>246</v>
       </c>
       <c r="B437" s="4">
         <v>10000</v>
@@ -7491,8 +7630,8 @@
       <c r="I437"/>
     </row>
     <row r="438" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A438" s="13" t="s">
-        <v>283</v>
+      <c r="A438" s="12" t="s">
+        <v>247</v>
       </c>
       <c r="B438" s="4">
         <v>8000</v>
@@ -7503,8 +7642,8 @@
       <c r="I438"/>
     </row>
     <row r="439" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A439" s="13" t="s">
-        <v>284</v>
+      <c r="A439" s="12" t="s">
+        <v>248</v>
       </c>
       <c r="B439" s="4">
         <v>12000</v>
@@ -7515,8 +7654,8 @@
       <c r="I439"/>
     </row>
     <row r="440" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A440" s="13" t="s">
-        <v>285</v>
+      <c r="A440" s="12" t="s">
+        <v>249</v>
       </c>
       <c r="B440" s="4">
         <v>10000</v>
@@ -7527,8 +7666,8 @@
       <c r="I440"/>
     </row>
     <row r="441" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A441" s="13" t="s">
-        <v>286</v>
+      <c r="A441" s="12" t="s">
+        <v>250</v>
       </c>
       <c r="B441" s="4">
         <v>8000</v>
@@ -7539,8 +7678,8 @@
       <c r="I441"/>
     </row>
     <row r="442" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A442" s="13" t="s">
-        <v>287</v>
+      <c r="A442" s="12" t="s">
+        <v>251</v>
       </c>
       <c r="B442" s="4">
         <v>12000</v>
@@ -7551,8 +7690,8 @@
       <c r="I442"/>
     </row>
     <row r="443" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A443" s="13" t="s">
-        <v>288</v>
+      <c r="A443" s="12" t="s">
+        <v>252</v>
       </c>
       <c r="B443" s="4">
         <v>10000</v>
@@ -7563,8 +7702,8 @@
       <c r="I443"/>
     </row>
     <row r="444" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A444" s="13" t="s">
-        <v>289</v>
+      <c r="A444" s="12" t="s">
+        <v>253</v>
       </c>
       <c r="B444" s="4">
         <v>8000</v>
@@ -7575,8 +7714,8 @@
       <c r="I444"/>
     </row>
     <row r="445" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A445" s="13" t="s">
-        <v>290</v>
+      <c r="A445" s="12" t="s">
+        <v>254</v>
       </c>
       <c r="B445" s="4">
         <v>12000</v>
@@ -7587,8 +7726,8 @@
       <c r="I445"/>
     </row>
     <row r="446" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A446" s="13" t="s">
-        <v>291</v>
+      <c r="A446" s="12" t="s">
+        <v>255</v>
       </c>
       <c r="B446" s="4">
         <v>10000</v>
@@ -7599,8 +7738,8 @@
       <c r="I446"/>
     </row>
     <row r="447" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A447" s="13" t="s">
-        <v>292</v>
+      <c r="A447" s="12" t="s">
+        <v>256</v>
       </c>
       <c r="B447" s="4">
         <v>8000</v>
@@ -7611,8 +7750,8 @@
       <c r="I447"/>
     </row>
     <row r="448" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A448" s="13" t="s">
-        <v>293</v>
+      <c r="A448" s="12" t="s">
+        <v>257</v>
       </c>
       <c r="B448" s="4">
         <v>12000</v>
@@ -7623,8 +7762,8 @@
       <c r="I448"/>
     </row>
     <row r="449" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A449" s="13" t="s">
-        <v>294</v>
+      <c r="A449" s="12" t="s">
+        <v>258</v>
       </c>
       <c r="B449" s="4">
         <v>10000</v>
@@ -7635,8 +7774,8 @@
       <c r="I449"/>
     </row>
     <row r="450" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A450" s="13" t="s">
-        <v>295</v>
+      <c r="A450" s="12" t="s">
+        <v>259</v>
       </c>
       <c r="B450" s="4">
         <v>8000</v>
@@ -7647,8 +7786,8 @@
       <c r="I450"/>
     </row>
     <row r="451" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A451" s="13" t="s">
-        <v>296</v>
+      <c r="A451" s="12" t="s">
+        <v>260</v>
       </c>
       <c r="B451" s="4">
         <v>12000</v>
@@ -7659,8 +7798,8 @@
       <c r="I451"/>
     </row>
     <row r="452" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A452" s="13" t="s">
-        <v>297</v>
+      <c r="A452" s="12" t="s">
+        <v>261</v>
       </c>
       <c r="B452" s="4">
         <v>10000</v>
@@ -7671,8 +7810,8 @@
       <c r="I452"/>
     </row>
     <row r="453" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A453" s="13" t="s">
-        <v>298</v>
+      <c r="A453" s="12" t="s">
+        <v>262</v>
       </c>
       <c r="B453" s="4">
         <v>8000</v>
@@ -7683,8 +7822,8 @@
       <c r="I453"/>
     </row>
     <row r="454" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A454" s="13" t="s">
-        <v>299</v>
+      <c r="A454" s="12" t="s">
+        <v>263</v>
       </c>
       <c r="B454" s="4">
         <v>12000</v>
@@ -7695,1529 +7834,1864 @@
       <c r="I454"/>
     </row>
     <row r="455" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A455" s="13" t="s">
+      <c r="A455" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="B455" s="4">
+        <v>10000</v>
+      </c>
+      <c r="C455" s="2">
+        <v>1800</v>
+      </c>
+      <c r="I455"/>
+    </row>
+    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A456" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="B456" s="4">
+        <v>8000</v>
+      </c>
+      <c r="C456" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I456"/>
+    </row>
+    <row r="457" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A457" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="B457" s="4">
+        <v>12000</v>
+      </c>
+      <c r="C457" s="2">
+        <v>2000</v>
+      </c>
+      <c r="I457"/>
+    </row>
+    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A458" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="B458" s="4">
+        <v>10000</v>
+      </c>
+      <c r="C458" s="2">
+        <v>1800</v>
+      </c>
+      <c r="I458"/>
+    </row>
+    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A459" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="B459" s="4">
+        <v>8000</v>
+      </c>
+      <c r="C459" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I459"/>
+    </row>
+    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A460" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="B460" s="4">
+        <v>12000</v>
+      </c>
+      <c r="C460" s="2">
+        <v>2000</v>
+      </c>
+      <c r="I460"/>
+    </row>
+    <row r="461" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A461" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="B461" s="4">
+        <v>10000</v>
+      </c>
+      <c r="C461" s="2">
+        <v>1800</v>
+      </c>
+      <c r="I461"/>
+    </row>
+    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A462" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="B462" s="4">
+        <v>8000</v>
+      </c>
+      <c r="C462" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I462"/>
+    </row>
+    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A463" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="B463" s="4">
+        <v>12000</v>
+      </c>
+      <c r="C463" s="2">
+        <v>2000</v>
+      </c>
+      <c r="I463"/>
+    </row>
+    <row r="464" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A464" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="B464" s="4">
+        <v>10000</v>
+      </c>
+      <c r="C464" s="2">
+        <v>1800</v>
+      </c>
+      <c r="I464"/>
+    </row>
+    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A465" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="B465" s="4">
+        <v>8000</v>
+      </c>
+      <c r="C465" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I465"/>
+    </row>
+    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A466" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="B466" s="4">
+        <v>12000</v>
+      </c>
+      <c r="C466" s="2">
+        <v>2000</v>
+      </c>
+      <c r="I466"/>
+    </row>
+    <row r="467" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A467" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="B467" s="4">
+        <v>10000</v>
+      </c>
+      <c r="C467" s="2">
+        <v>1800</v>
+      </c>
+      <c r="I467"/>
+    </row>
+    <row r="468" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A468" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="B468" s="4">
+        <v>8000</v>
+      </c>
+      <c r="C468" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I468"/>
+    </row>
+    <row r="469" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A469" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="B469" s="4">
+        <v>12000</v>
+      </c>
+      <c r="C469" s="2">
+        <v>2000</v>
+      </c>
+      <c r="I469"/>
+    </row>
+    <row r="470" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A470" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="B470" s="4">
+        <v>10000</v>
+      </c>
+      <c r="C470" s="2">
+        <v>1800</v>
+      </c>
+      <c r="I470"/>
+    </row>
+    <row r="471" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A471" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="B471" s="4">
+        <v>8000</v>
+      </c>
+      <c r="C471" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I471"/>
+    </row>
+    <row r="472" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A472" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="B472" s="4">
+        <v>12000</v>
+      </c>
+      <c r="C472" s="2">
+        <v>2000</v>
+      </c>
+      <c r="I472"/>
+    </row>
+    <row r="473" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A473" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="B473" s="4">
+        <v>10000</v>
+      </c>
+      <c r="C473" s="2">
+        <v>1800</v>
+      </c>
+      <c r="I473"/>
+    </row>
+    <row r="474" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A474" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="B474" s="4">
+        <v>8000</v>
+      </c>
+      <c r="C474" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I474"/>
+    </row>
+    <row r="475" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A475" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="B475" s="4">
+        <v>12000</v>
+      </c>
+      <c r="C475" s="2">
+        <v>2000</v>
+      </c>
+      <c r="I475"/>
+    </row>
+    <row r="476" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A476" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="B476" s="4">
+        <v>10000</v>
+      </c>
+      <c r="C476" s="2">
+        <v>1800</v>
+      </c>
+      <c r="I476"/>
+    </row>
+    <row r="477" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A477" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="B477" s="4">
+        <v>8000</v>
+      </c>
+      <c r="C477" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I477"/>
+    </row>
+    <row r="478" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A478" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="B478" s="4">
+        <v>12000</v>
+      </c>
+      <c r="C478" s="2">
+        <v>2000</v>
+      </c>
+      <c r="I478"/>
+    </row>
+    <row r="479" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A479" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="B479" s="4">
+        <v>10000</v>
+      </c>
+      <c r="C479" s="2">
+        <v>1800</v>
+      </c>
+      <c r="I479"/>
+    </row>
+    <row r="480" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A480" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="B480" s="4">
+        <v>8000</v>
+      </c>
+      <c r="C480" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I480"/>
+    </row>
+    <row r="481" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A481" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="B481" s="4">
+        <v>12000</v>
+      </c>
+      <c r="C481" s="2">
+        <v>2000</v>
+      </c>
+      <c r="I481"/>
+    </row>
+    <row r="482" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A482" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="B482" s="4">
+        <v>10000</v>
+      </c>
+      <c r="C482" s="2">
+        <v>1800</v>
+      </c>
+      <c r="I482"/>
+    </row>
+    <row r="483" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A483" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="B483" s="4">
+        <v>8000</v>
+      </c>
+      <c r="C483" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I483"/>
+    </row>
+    <row r="484" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A484" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="B484" s="4">
+        <v>12000</v>
+      </c>
+      <c r="C484" s="2">
+        <v>2000</v>
+      </c>
+      <c r="I484"/>
+    </row>
+    <row r="485" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A485" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="B485" s="4">
+        <v>10000</v>
+      </c>
+      <c r="C485" s="2">
+        <v>1800</v>
+      </c>
+      <c r="I485"/>
+    </row>
+    <row r="486" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A486" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="B486" s="4">
+        <v>8000</v>
+      </c>
+      <c r="C486" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I486"/>
+    </row>
+    <row r="487" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A487" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="B487" s="4">
+        <v>12000</v>
+      </c>
+      <c r="C487" s="2">
+        <v>2000</v>
+      </c>
+      <c r="I487"/>
+    </row>
+    <row r="488" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A488" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="B488" s="4">
+        <v>10000</v>
+      </c>
+      <c r="C488" s="2">
+        <v>1800</v>
+      </c>
+      <c r="I488"/>
+    </row>
+    <row r="489" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A489" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="B489" s="4">
+        <v>8000</v>
+      </c>
+      <c r="C489" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I489"/>
+    </row>
+    <row r="490" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A490" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="B490" s="4">
+        <v>12000</v>
+      </c>
+      <c r="C490" s="2">
+        <v>2000</v>
+      </c>
+      <c r="I490"/>
+    </row>
+    <row r="491" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A491" s="12" t="s">
         <v>300</v>
-      </c>
-      <c r="B455" s="4"/>
-      <c r="C455" s="2"/>
-      <c r="I455"/>
-    </row>
-    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A456" s="13" t="s">
-        <v>301</v>
-      </c>
-      <c r="B456" s="4"/>
-      <c r="C456" s="2"/>
-      <c r="I456"/>
-    </row>
-    <row r="457" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A457" s="13" t="s">
-        <v>302</v>
-      </c>
-      <c r="B457" s="4"/>
-      <c r="C457" s="2"/>
-      <c r="I457"/>
-    </row>
-    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A458" s="13" t="s">
-        <v>303</v>
-      </c>
-      <c r="B458" s="4"/>
-      <c r="C458" s="2"/>
-      <c r="I458"/>
-    </row>
-    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A459" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="B459" s="4"/>
-      <c r="C459" s="2"/>
-      <c r="I459"/>
-    </row>
-    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A460" s="13" t="s">
-        <v>305</v>
-      </c>
-      <c r="B460" s="4"/>
-      <c r="C460" s="2"/>
-      <c r="I460"/>
-    </row>
-    <row r="461" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A461" s="13" t="s">
-        <v>306</v>
-      </c>
-      <c r="B461" s="4"/>
-      <c r="C461" s="2"/>
-      <c r="I461"/>
-    </row>
-    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A462" s="13" t="s">
-        <v>307</v>
-      </c>
-      <c r="B462" s="4"/>
-      <c r="C462" s="2"/>
-      <c r="I462"/>
-    </row>
-    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A463" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="B463" s="4"/>
-      <c r="C463" s="2"/>
-      <c r="I463"/>
-    </row>
-    <row r="464" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A464" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="B464" s="4"/>
-      <c r="C464" s="2"/>
-      <c r="I464"/>
-    </row>
-    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A465" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="B465" s="4"/>
-      <c r="C465" s="2"/>
-      <c r="I465"/>
-    </row>
-    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A466" s="13" t="s">
-        <v>311</v>
-      </c>
-      <c r="B466" s="4"/>
-      <c r="C466" s="2"/>
-      <c r="I466"/>
-    </row>
-    <row r="467" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A467" s="13" t="s">
-        <v>312</v>
-      </c>
-      <c r="B467" s="4"/>
-      <c r="C467" s="2"/>
-      <c r="I467"/>
-    </row>
-    <row r="468" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A468" s="13" t="s">
-        <v>313</v>
-      </c>
-      <c r="B468" s="4"/>
-      <c r="C468" s="2"/>
-      <c r="I468"/>
-    </row>
-    <row r="469" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A469" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="B469" s="4"/>
-      <c r="C469" s="2"/>
-      <c r="I469"/>
-    </row>
-    <row r="470" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A470" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="B470" s="4"/>
-      <c r="C470" s="2"/>
-      <c r="I470"/>
-    </row>
-    <row r="471" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A471" s="13" t="s">
-        <v>316</v>
-      </c>
-      <c r="B471" s="4"/>
-      <c r="C471" s="2"/>
-      <c r="I471"/>
-    </row>
-    <row r="472" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A472" s="13" t="s">
-        <v>317</v>
-      </c>
-      <c r="B472" s="4"/>
-      <c r="C472" s="2"/>
-      <c r="I472"/>
-    </row>
-    <row r="473" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A473" s="13" t="s">
-        <v>318</v>
-      </c>
-      <c r="B473" s="4"/>
-      <c r="C473" s="2"/>
-      <c r="I473"/>
-    </row>
-    <row r="474" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A474" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="B474" s="4"/>
-      <c r="C474" s="2"/>
-      <c r="I474"/>
-    </row>
-    <row r="475" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A475" s="13" t="s">
-        <v>320</v>
-      </c>
-      <c r="B475" s="4"/>
-      <c r="C475" s="2"/>
-      <c r="I475"/>
-    </row>
-    <row r="476" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A476" s="13" t="s">
-        <v>321</v>
-      </c>
-      <c r="B476" s="4"/>
-      <c r="C476" s="2"/>
-      <c r="I476"/>
-    </row>
-    <row r="477" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A477" s="13" t="s">
-        <v>322</v>
-      </c>
-      <c r="B477" s="4"/>
-      <c r="C477" s="2"/>
-      <c r="I477"/>
-    </row>
-    <row r="478" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A478" s="13" t="s">
-        <v>323</v>
-      </c>
-      <c r="B478" s="4"/>
-      <c r="C478" s="2"/>
-      <c r="I478"/>
-    </row>
-    <row r="479" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A479" s="13" t="s">
-        <v>324</v>
-      </c>
-      <c r="B479" s="4"/>
-      <c r="C479" s="2"/>
-      <c r="I479"/>
-    </row>
-    <row r="480" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A480" s="13" t="s">
-        <v>325</v>
-      </c>
-      <c r="B480" s="4"/>
-      <c r="C480" s="2"/>
-      <c r="I480"/>
-    </row>
-    <row r="481" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A481" s="13" t="s">
-        <v>326</v>
-      </c>
-      <c r="B481" s="4"/>
-      <c r="C481" s="2"/>
-      <c r="I481"/>
-    </row>
-    <row r="482" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A482" s="13" t="s">
-        <v>327</v>
-      </c>
-      <c r="B482" s="4"/>
-      <c r="C482" s="2"/>
-      <c r="I482"/>
-    </row>
-    <row r="483" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A483" s="13" t="s">
-        <v>328</v>
-      </c>
-      <c r="B483" s="4"/>
-      <c r="C483" s="2"/>
-      <c r="I483"/>
-    </row>
-    <row r="484" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A484" s="13" t="s">
-        <v>329</v>
-      </c>
-      <c r="B484" s="4"/>
-      <c r="C484" s="2"/>
-      <c r="I484"/>
-    </row>
-    <row r="485" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A485" s="13" t="s">
-        <v>330</v>
-      </c>
-      <c r="B485" s="4"/>
-      <c r="C485" s="2"/>
-      <c r="I485"/>
-    </row>
-    <row r="486" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A486" s="13" t="s">
-        <v>331</v>
-      </c>
-      <c r="B486" s="4"/>
-      <c r="C486" s="2"/>
-      <c r="I486"/>
-    </row>
-    <row r="487" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A487" s="13" t="s">
-        <v>332</v>
-      </c>
-      <c r="B487" s="4"/>
-      <c r="C487" s="2"/>
-      <c r="I487"/>
-    </row>
-    <row r="488" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A488" s="13" t="s">
-        <v>333</v>
-      </c>
-      <c r="B488" s="4"/>
-      <c r="C488" s="2"/>
-      <c r="I488"/>
-    </row>
-    <row r="489" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A489" s="13" t="s">
-        <v>334</v>
-      </c>
-      <c r="B489" s="4"/>
-      <c r="C489" s="2"/>
-      <c r="I489"/>
-    </row>
-    <row r="490" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A490" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="B490" s="4"/>
-      <c r="C490" s="2"/>
-      <c r="I490"/>
-    </row>
-    <row r="491" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A491" s="13" t="s">
-        <v>336</v>
       </c>
       <c r="B491" s="4"/>
       <c r="C491" s="2"/>
       <c r="I491"/>
     </row>
     <row r="492" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A492" s="13" t="s">
-        <v>337</v>
+      <c r="A492" s="12" t="s">
+        <v>301</v>
       </c>
       <c r="B492" s="4"/>
       <c r="C492" s="2"/>
       <c r="I492"/>
     </row>
     <row r="493" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A493" s="13" t="s">
-        <v>338</v>
+      <c r="A493" s="12" t="s">
+        <v>302</v>
       </c>
       <c r="B493" s="4"/>
       <c r="C493" s="2"/>
       <c r="I493"/>
     </row>
     <row r="494" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A494" s="13" t="s">
-        <v>339</v>
+      <c r="A494" s="12" t="s">
+        <v>303</v>
       </c>
       <c r="B494" s="4"/>
       <c r="C494" s="2"/>
       <c r="I494"/>
     </row>
     <row r="495" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A495" s="13" t="s">
-        <v>340</v>
+      <c r="A495" s="12" t="s">
+        <v>304</v>
       </c>
       <c r="B495" s="4"/>
       <c r="C495" s="2"/>
       <c r="I495"/>
     </row>
     <row r="496" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A496" s="13" t="s">
-        <v>341</v>
+      <c r="A496" s="12" t="s">
+        <v>305</v>
       </c>
       <c r="B496" s="4"/>
       <c r="C496" s="2"/>
       <c r="I496"/>
     </row>
     <row r="497" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A497" s="13" t="s">
-        <v>342</v>
+      <c r="A497" s="12" t="s">
+        <v>306</v>
       </c>
       <c r="B497" s="4"/>
       <c r="C497" s="2"/>
       <c r="I497"/>
     </row>
     <row r="498" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A498" s="13" t="s">
-        <v>343</v>
+      <c r="A498" s="12" t="s">
+        <v>307</v>
       </c>
       <c r="B498" s="4"/>
       <c r="C498" s="2"/>
       <c r="I498"/>
     </row>
     <row r="499" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A499" s="13" t="s">
-        <v>344</v>
+      <c r="A499" s="12" t="s">
+        <v>308</v>
       </c>
       <c r="B499" s="4"/>
       <c r="C499" s="2"/>
       <c r="I499"/>
     </row>
     <row r="500" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A500" s="13" t="s">
-        <v>345</v>
+      <c r="A500" s="12" t="s">
+        <v>309</v>
       </c>
       <c r="B500" s="4"/>
       <c r="C500" s="2"/>
       <c r="I500"/>
     </row>
     <row r="501" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A501" s="13" t="s">
-        <v>346</v>
+      <c r="A501" s="12" t="s">
+        <v>310</v>
       </c>
       <c r="B501" s="4"/>
       <c r="C501" s="2"/>
       <c r="I501"/>
     </row>
     <row r="502" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A502" s="13" t="s">
-        <v>347</v>
+      <c r="A502" s="12" t="s">
+        <v>311</v>
       </c>
       <c r="B502" s="4"/>
       <c r="C502" s="2"/>
       <c r="I502"/>
     </row>
     <row r="503" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A503" s="13" t="s">
-        <v>348</v>
+      <c r="A503" s="12" t="s">
+        <v>312</v>
       </c>
       <c r="B503" s="4"/>
       <c r="C503" s="2"/>
       <c r="I503"/>
     </row>
     <row r="504" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A504" s="13" t="s">
-        <v>349</v>
+      <c r="A504" s="12" t="s">
+        <v>313</v>
       </c>
       <c r="B504" s="4"/>
       <c r="C504" s="2"/>
       <c r="I504"/>
     </row>
     <row r="505" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A505" s="13" t="s">
-        <v>350</v>
+      <c r="A505" s="12" t="s">
+        <v>314</v>
       </c>
       <c r="B505" s="4"/>
       <c r="C505" s="2"/>
       <c r="I505"/>
     </row>
     <row r="506" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A506" s="13" t="s">
-        <v>351</v>
+      <c r="A506" s="12" t="s">
+        <v>315</v>
       </c>
       <c r="B506" s="4"/>
       <c r="C506" s="2"/>
       <c r="I506"/>
     </row>
     <row r="507" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A507" s="13" t="s">
-        <v>352</v>
+      <c r="A507" s="12" t="s">
+        <v>316</v>
       </c>
       <c r="B507" s="4"/>
       <c r="C507" s="2"/>
       <c r="I507"/>
     </row>
     <row r="508" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A508" s="13" t="s">
-        <v>353</v>
+      <c r="A508" s="12" t="s">
+        <v>317</v>
       </c>
       <c r="B508" s="4"/>
       <c r="C508" s="2"/>
       <c r="I508"/>
     </row>
     <row r="509" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A509" s="13" t="s">
-        <v>354</v>
+      <c r="A509" s="12" t="s">
+        <v>318</v>
       </c>
       <c r="B509" s="4"/>
       <c r="C509" s="2"/>
       <c r="I509"/>
     </row>
     <row r="510" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A510" s="13" t="s">
-        <v>355</v>
+      <c r="A510" s="12" t="s">
+        <v>319</v>
       </c>
       <c r="B510" s="4"/>
       <c r="C510" s="2"/>
       <c r="I510"/>
     </row>
     <row r="511" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A511" s="13" t="s">
-        <v>356</v>
+      <c r="A511" s="12" t="s">
+        <v>320</v>
       </c>
       <c r="B511" s="4"/>
       <c r="C511" s="2"/>
       <c r="I511"/>
     </row>
     <row r="512" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A512" s="13" t="s">
-        <v>357</v>
+      <c r="A512" s="12" t="s">
+        <v>321</v>
       </c>
       <c r="B512" s="4"/>
       <c r="C512" s="2"/>
       <c r="I512"/>
     </row>
     <row r="513" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A513" s="13" t="s">
-        <v>358</v>
+      <c r="A513" s="12" t="s">
+        <v>322</v>
       </c>
       <c r="B513" s="4"/>
       <c r="C513" s="2"/>
       <c r="I513"/>
     </row>
     <row r="514" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A514" s="13" t="s">
-        <v>359</v>
+      <c r="A514" s="12" t="s">
+        <v>323</v>
       </c>
       <c r="B514" s="4"/>
       <c r="C514" s="2"/>
       <c r="I514"/>
     </row>
     <row r="515" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A515" s="13" t="s">
-        <v>360</v>
+      <c r="A515" s="12" t="s">
+        <v>324</v>
       </c>
       <c r="B515" s="4"/>
       <c r="C515" s="2"/>
       <c r="I515"/>
     </row>
     <row r="516" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A516" s="13" t="s">
-        <v>361</v>
+      <c r="A516" s="12" t="s">
+        <v>325</v>
       </c>
       <c r="B516" s="4"/>
       <c r="C516" s="2"/>
       <c r="I516"/>
     </row>
     <row r="517" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A517" s="13" t="s">
-        <v>362</v>
+      <c r="A517" s="12" t="s">
+        <v>326</v>
       </c>
       <c r="B517" s="4"/>
       <c r="C517" s="2"/>
       <c r="I517"/>
     </row>
     <row r="518" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A518" s="13" t="s">
-        <v>363</v>
+      <c r="A518" s="12" t="s">
+        <v>327</v>
       </c>
       <c r="B518" s="4"/>
       <c r="C518" s="2"/>
       <c r="I518"/>
     </row>
     <row r="519" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A519" s="13" t="s">
-        <v>364</v>
+      <c r="A519" s="12" t="s">
+        <v>328</v>
       </c>
       <c r="B519" s="4"/>
       <c r="C519" s="2"/>
       <c r="I519"/>
     </row>
     <row r="520" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A520" s="13" t="s">
-        <v>365</v>
+      <c r="A520" s="12" t="s">
+        <v>329</v>
       </c>
       <c r="B520" s="4"/>
       <c r="C520" s="2"/>
       <c r="I520"/>
     </row>
     <row r="521" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A521" s="13" t="s">
-        <v>366</v>
+      <c r="A521" s="12" t="s">
+        <v>330</v>
       </c>
       <c r="B521" s="4"/>
       <c r="C521" s="2"/>
       <c r="I521"/>
     </row>
     <row r="522" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A522" s="13" t="s">
-        <v>367</v>
+      <c r="A522" s="12" t="s">
+        <v>331</v>
       </c>
       <c r="B522" s="4"/>
       <c r="C522" s="2"/>
       <c r="I522"/>
     </row>
     <row r="523" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A523" s="13" t="s">
-        <v>368</v>
+      <c r="A523" s="12" t="s">
+        <v>332</v>
       </c>
       <c r="B523" s="4"/>
       <c r="C523" s="2"/>
       <c r="I523"/>
     </row>
     <row r="524" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A524" s="13" t="s">
-        <v>369</v>
+      <c r="A524" s="12" t="s">
+        <v>333</v>
       </c>
       <c r="B524" s="4"/>
       <c r="C524" s="2"/>
       <c r="I524"/>
     </row>
     <row r="525" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A525" s="13" t="s">
-        <v>370</v>
+      <c r="A525" s="12" t="s">
+        <v>334</v>
       </c>
       <c r="B525" s="4"/>
       <c r="C525" s="2"/>
       <c r="I525"/>
     </row>
     <row r="526" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A526" s="13" t="s">
-        <v>371</v>
+      <c r="A526" s="12" t="s">
+        <v>335</v>
       </c>
       <c r="B526" s="4"/>
       <c r="C526" s="2"/>
       <c r="I526"/>
     </row>
     <row r="527" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A527" s="13" t="s">
-        <v>372</v>
+      <c r="A527" s="12" t="s">
+        <v>336</v>
       </c>
       <c r="B527" s="4"/>
       <c r="C527" s="2"/>
       <c r="I527"/>
     </row>
     <row r="528" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A528" s="13" t="s">
-        <v>373</v>
-      </c>
+      <c r="A528" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="B528" s="4"/>
       <c r="C528" s="2"/>
       <c r="I528"/>
     </row>
     <row r="529" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A529" s="13" t="s">
-        <v>374</v>
-      </c>
+      <c r="A529" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="B529" s="4"/>
       <c r="C529" s="2"/>
       <c r="I529"/>
     </row>
     <row r="530" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A530" s="13" t="s">
-        <v>375</v>
-      </c>
+      <c r="A530" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="B530" s="4"/>
       <c r="C530" s="2"/>
       <c r="I530"/>
     </row>
     <row r="531" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A531" s="13" t="s">
-        <v>376</v>
-      </c>
+      <c r="A531" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="B531" s="4"/>
       <c r="C531" s="2"/>
       <c r="I531"/>
     </row>
     <row r="532" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A532" s="13" t="s">
-        <v>377</v>
-      </c>
+      <c r="A532" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="B532" s="4"/>
       <c r="C532" s="2"/>
       <c r="I532"/>
     </row>
     <row r="533" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A533" s="13" t="s">
-        <v>378</v>
-      </c>
+      <c r="A533" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="B533" s="4"/>
       <c r="C533" s="2"/>
       <c r="I533"/>
     </row>
     <row r="534" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A534" s="13" t="s">
-        <v>379</v>
-      </c>
+      <c r="A534" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="B534" s="4"/>
       <c r="C534" s="2"/>
       <c r="I534"/>
     </row>
     <row r="535" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A535" s="13" t="s">
-        <v>380</v>
-      </c>
+      <c r="A535" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="B535" s="4"/>
       <c r="C535" s="2"/>
       <c r="I535"/>
     </row>
     <row r="536" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A536" s="13" t="s">
-        <v>381</v>
-      </c>
+      <c r="A536" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="B536" s="4"/>
       <c r="C536" s="2"/>
       <c r="I536"/>
     </row>
     <row r="537" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A537" s="13" t="s">
-        <v>382</v>
-      </c>
+      <c r="A537" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="B537" s="4"/>
       <c r="C537" s="2"/>
       <c r="I537"/>
     </row>
     <row r="538" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A538" s="13" t="s">
-        <v>383</v>
-      </c>
+      <c r="A538" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="B538" s="4"/>
       <c r="C538" s="2"/>
       <c r="I538"/>
     </row>
     <row r="539" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A539" s="13" t="s">
-        <v>384</v>
-      </c>
+      <c r="A539" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="B539" s="4"/>
       <c r="C539" s="2"/>
       <c r="I539"/>
     </row>
     <row r="540" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A540" s="13" t="s">
-        <v>385</v>
-      </c>
+      <c r="A540" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="B540" s="4"/>
       <c r="C540" s="2"/>
       <c r="I540"/>
     </row>
     <row r="541" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A541" s="13" t="s">
-        <v>386</v>
-      </c>
+      <c r="A541" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="B541" s="4"/>
       <c r="C541" s="2"/>
       <c r="I541"/>
     </row>
     <row r="542" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A542" s="13" t="s">
-        <v>387</v>
-      </c>
+      <c r="A542" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="B542" s="4"/>
       <c r="C542" s="2"/>
       <c r="I542"/>
     </row>
     <row r="543" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A543" s="13" t="s">
-        <v>388</v>
-      </c>
+      <c r="A543" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="B543" s="4"/>
       <c r="C543" s="2"/>
       <c r="I543"/>
     </row>
     <row r="544" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A544" s="13" t="s">
-        <v>389</v>
-      </c>
+      <c r="A544" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="B544" s="4"/>
       <c r="C544" s="2"/>
       <c r="I544"/>
     </row>
     <row r="545" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A545" s="13" t="s">
-        <v>390</v>
-      </c>
+      <c r="A545" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="B545" s="4"/>
       <c r="C545" s="2"/>
       <c r="I545"/>
     </row>
     <row r="546" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A546" s="13" t="s">
-        <v>391</v>
-      </c>
+      <c r="A546" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="B546" s="4"/>
       <c r="C546" s="2"/>
       <c r="I546"/>
     </row>
     <row r="547" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A547" s="13" t="s">
-        <v>392</v>
-      </c>
+      <c r="A547" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="B547" s="4"/>
       <c r="C547" s="2"/>
       <c r="I547"/>
     </row>
     <row r="548" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A548" s="13" t="s">
-        <v>393</v>
-      </c>
+      <c r="A548" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="B548" s="4"/>
       <c r="C548" s="2"/>
       <c r="I548"/>
     </row>
     <row r="549" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A549" s="13" t="s">
-        <v>394</v>
-      </c>
+      <c r="A549" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="B549" s="4"/>
       <c r="C549" s="2"/>
       <c r="I549"/>
     </row>
     <row r="550" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A550" s="13" t="s">
-        <v>395</v>
-      </c>
+      <c r="A550" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="B550" s="4"/>
       <c r="C550" s="2"/>
       <c r="I550"/>
     </row>
     <row r="551" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A551" s="13" t="s">
-        <v>396</v>
-      </c>
+      <c r="A551" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="B551" s="4"/>
       <c r="C551" s="2"/>
       <c r="I551"/>
     </row>
     <row r="552" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A552" s="13" t="s">
-        <v>397</v>
-      </c>
+      <c r="A552" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="B552" s="4"/>
       <c r="C552" s="2"/>
       <c r="I552"/>
     </row>
     <row r="553" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A553" s="13" t="s">
-        <v>398</v>
-      </c>
+      <c r="A553" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="B553" s="4"/>
       <c r="C553" s="2"/>
       <c r="I553"/>
     </row>
     <row r="554" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A554" s="13" t="s">
-        <v>399</v>
-      </c>
+      <c r="A554" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="B554" s="4"/>
       <c r="C554" s="2"/>
       <c r="I554"/>
     </row>
     <row r="555" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A555" s="13" t="s">
-        <v>400</v>
-      </c>
+      <c r="A555" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="B555" s="4"/>
       <c r="C555" s="2"/>
       <c r="I555"/>
     </row>
     <row r="556" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A556" s="13" t="s">
-        <v>401</v>
-      </c>
+      <c r="A556" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="B556" s="4"/>
       <c r="C556" s="2"/>
       <c r="I556"/>
     </row>
     <row r="557" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A557" s="13" t="s">
-        <v>402</v>
-      </c>
+      <c r="A557" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="B557" s="4"/>
       <c r="C557" s="2"/>
       <c r="I557"/>
     </row>
     <row r="558" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A558" s="13" t="s">
-        <v>403</v>
-      </c>
+      <c r="A558" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="B558" s="4"/>
       <c r="C558" s="2"/>
       <c r="I558"/>
     </row>
     <row r="559" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A559" s="13" t="s">
-        <v>404</v>
-      </c>
+      <c r="A559" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="B559" s="4"/>
       <c r="C559" s="2"/>
       <c r="I559"/>
     </row>
     <row r="560" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A560" s="13" t="s">
-        <v>405</v>
-      </c>
+      <c r="A560" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="B560" s="4"/>
       <c r="C560" s="2"/>
       <c r="I560"/>
     </row>
     <row r="561" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A561" s="13" t="s">
-        <v>406</v>
-      </c>
+      <c r="A561" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="B561" s="4"/>
       <c r="C561" s="2"/>
       <c r="I561"/>
     </row>
     <row r="562" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A562" s="13" t="s">
-        <v>407</v>
-      </c>
+      <c r="A562" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="B562" s="4"/>
       <c r="C562" s="2"/>
       <c r="I562"/>
     </row>
     <row r="563" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A563" s="13" t="s">
-        <v>408</v>
-      </c>
+      <c r="A563" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="B563" s="4"/>
       <c r="C563" s="2"/>
       <c r="I563"/>
     </row>
     <row r="564" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A564" s="13" t="s">
-        <v>409</v>
+      <c r="A564" s="12" t="s">
+        <v>373</v>
       </c>
       <c r="C564" s="2"/>
       <c r="I564"/>
     </row>
     <row r="565" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A565" s="13" t="s">
-        <v>410</v>
+      <c r="A565" s="12" t="s">
+        <v>374</v>
       </c>
       <c r="C565" s="2"/>
       <c r="I565"/>
     </row>
     <row r="566" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A566" s="13" t="s">
-        <v>411</v>
+      <c r="A566" s="12" t="s">
+        <v>375</v>
       </c>
       <c r="C566" s="2"/>
       <c r="I566"/>
     </row>
     <row r="567" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A567" s="13" t="s">
-        <v>412</v>
+      <c r="A567" s="12" t="s">
+        <v>376</v>
       </c>
       <c r="C567" s="2"/>
       <c r="I567"/>
     </row>
     <row r="568" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A568" s="13" t="s">
-        <v>413</v>
+      <c r="A568" s="12" t="s">
+        <v>377</v>
       </c>
       <c r="C568" s="2"/>
       <c r="I568"/>
     </row>
     <row r="569" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A569" s="13" t="s">
-        <v>414</v>
+      <c r="A569" s="12" t="s">
+        <v>378</v>
       </c>
       <c r="C569" s="2"/>
       <c r="I569"/>
     </row>
     <row r="570" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A570" s="13" t="s">
-        <v>415</v>
+      <c r="A570" s="12" t="s">
+        <v>379</v>
       </c>
       <c r="C570" s="2"/>
       <c r="I570"/>
     </row>
     <row r="571" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A571" s="13" t="s">
-        <v>416</v>
+      <c r="A571" s="12" t="s">
+        <v>380</v>
       </c>
       <c r="C571" s="2"/>
       <c r="I571"/>
     </row>
     <row r="572" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A572" s="13" t="s">
-        <v>417</v>
+      <c r="A572" s="12" t="s">
+        <v>381</v>
       </c>
       <c r="C572" s="2"/>
       <c r="I572"/>
     </row>
     <row r="573" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A573" s="13" t="s">
-        <v>418</v>
+      <c r="A573" s="12" t="s">
+        <v>382</v>
       </c>
       <c r="C573" s="2"/>
       <c r="I573"/>
     </row>
     <row r="574" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A574" s="13" t="s">
-        <v>419</v>
+      <c r="A574" s="12" t="s">
+        <v>383</v>
       </c>
       <c r="C574" s="2"/>
       <c r="I574"/>
     </row>
     <row r="575" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A575" s="13" t="s">
-        <v>420</v>
+      <c r="A575" s="12" t="s">
+        <v>384</v>
       </c>
       <c r="C575" s="2"/>
       <c r="I575"/>
     </row>
     <row r="576" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A576" s="13" t="s">
-        <v>421</v>
+      <c r="A576" s="12" t="s">
+        <v>385</v>
       </c>
       <c r="C576" s="2"/>
       <c r="I576"/>
     </row>
     <row r="577" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A577" s="13" t="s">
-        <v>422</v>
+      <c r="A577" s="12" t="s">
+        <v>386</v>
       </c>
       <c r="C577" s="2"/>
       <c r="I577"/>
     </row>
     <row r="578" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A578" s="13" t="s">
-        <v>423</v>
+      <c r="A578" s="12" t="s">
+        <v>387</v>
       </c>
       <c r="C578" s="2"/>
       <c r="I578"/>
     </row>
     <row r="579" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A579" s="13" t="s">
-        <v>424</v>
+      <c r="A579" s="12" t="s">
+        <v>388</v>
       </c>
       <c r="C579" s="2"/>
       <c r="I579"/>
     </row>
     <row r="580" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A580" s="13" t="s">
-        <v>425</v>
+      <c r="A580" s="12" t="s">
+        <v>389</v>
       </c>
       <c r="C580" s="2"/>
       <c r="I580"/>
     </row>
     <row r="581" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A581" s="13" t="s">
-        <v>426</v>
+      <c r="A581" s="12" t="s">
+        <v>390</v>
       </c>
       <c r="C581" s="2"/>
       <c r="I581"/>
     </row>
     <row r="582" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A582" s="13" t="s">
-        <v>427</v>
+      <c r="A582" s="12" t="s">
+        <v>391</v>
       </c>
       <c r="C582" s="2"/>
       <c r="I582"/>
     </row>
     <row r="583" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A583" s="13" t="s">
-        <v>428</v>
+      <c r="A583" s="12" t="s">
+        <v>392</v>
       </c>
       <c r="C583" s="2"/>
       <c r="I583"/>
     </row>
     <row r="584" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A584" s="13" t="s">
-        <v>429</v>
+      <c r="A584" s="12" t="s">
+        <v>393</v>
       </c>
       <c r="C584" s="2"/>
       <c r="I584"/>
     </row>
     <row r="585" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A585" s="13" t="s">
-        <v>430</v>
+      <c r="A585" s="12" t="s">
+        <v>394</v>
       </c>
       <c r="C585" s="2"/>
       <c r="I585"/>
     </row>
     <row r="586" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A586" s="13" t="s">
-        <v>431</v>
+      <c r="A586" s="12" t="s">
+        <v>395</v>
       </c>
       <c r="C586" s="2"/>
       <c r="I586"/>
     </row>
     <row r="587" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A587" s="13" t="s">
-        <v>432</v>
+      <c r="A587" s="12" t="s">
+        <v>396</v>
       </c>
       <c r="C587" s="2"/>
       <c r="I587"/>
     </row>
     <row r="588" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A588" s="13" t="s">
-        <v>433</v>
+      <c r="A588" s="12" t="s">
+        <v>397</v>
       </c>
       <c r="C588" s="2"/>
       <c r="I588"/>
     </row>
     <row r="589" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A589" s="13" t="s">
-        <v>434</v>
+      <c r="A589" s="12" t="s">
+        <v>398</v>
       </c>
       <c r="C589" s="2"/>
       <c r="I589"/>
     </row>
     <row r="590" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A590" s="13" t="s">
-        <v>435</v>
+      <c r="A590" s="12" t="s">
+        <v>399</v>
       </c>
       <c r="C590" s="2"/>
       <c r="I590"/>
     </row>
     <row r="591" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A591" s="13" t="s">
-        <v>436</v>
+      <c r="A591" s="12" t="s">
+        <v>400</v>
       </c>
       <c r="C591" s="2"/>
       <c r="I591"/>
     </row>
     <row r="592" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A592" s="13" t="s">
-        <v>437</v>
+      <c r="A592" s="12" t="s">
+        <v>401</v>
       </c>
       <c r="C592" s="2"/>
       <c r="I592"/>
     </row>
     <row r="593" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A593" s="13" t="s">
-        <v>438</v>
+      <c r="A593" s="12" t="s">
+        <v>402</v>
       </c>
       <c r="C593" s="2"/>
       <c r="I593"/>
     </row>
     <row r="594" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A594" s="13" t="s">
-        <v>439</v>
+      <c r="A594" s="12" t="s">
+        <v>403</v>
       </c>
       <c r="C594" s="2"/>
       <c r="I594"/>
     </row>
     <row r="595" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A595" s="13" t="s">
-        <v>440</v>
+      <c r="A595" s="12" t="s">
+        <v>404</v>
       </c>
       <c r="C595" s="2"/>
       <c r="I595"/>
     </row>
     <row r="596" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A596" s="13" t="s">
-        <v>441</v>
+      <c r="A596" s="12" t="s">
+        <v>405</v>
       </c>
       <c r="C596" s="2"/>
       <c r="I596"/>
     </row>
     <row r="597" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A597" s="13" t="s">
-        <v>442</v>
+      <c r="A597" s="12" t="s">
+        <v>406</v>
       </c>
       <c r="C597" s="2"/>
       <c r="I597"/>
     </row>
     <row r="598" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A598" s="13" t="s">
-        <v>443</v>
+      <c r="A598" s="12" t="s">
+        <v>407</v>
       </c>
       <c r="C598" s="2"/>
       <c r="I598"/>
     </row>
     <row r="599" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A599" s="5" t="s">
-        <v>632</v>
-      </c>
-      <c r="C599" s="2">
-        <v>3500</v>
-      </c>
+      <c r="A599" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="C599" s="2"/>
       <c r="I599"/>
     </row>
     <row r="600" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A600" s="5" t="s">
-        <v>633</v>
-      </c>
-      <c r="C600" s="2">
-        <v>3500</v>
-      </c>
+      <c r="A600" s="12" t="s">
+        <v>409</v>
+      </c>
+      <c r="C600" s="2"/>
       <c r="I600"/>
     </row>
     <row r="601" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A601" s="5" t="s">
-        <v>634</v>
-      </c>
-      <c r="C601" s="2">
-        <v>3500</v>
-      </c>
+      <c r="A601" s="12" t="s">
+        <v>410</v>
+      </c>
+      <c r="C601" s="2"/>
       <c r="I601"/>
     </row>
     <row r="602" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A602" s="5" t="s">
-        <v>635</v>
-      </c>
-      <c r="C602" s="2">
-        <v>3500</v>
-      </c>
+      <c r="A602" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="C602" s="2"/>
       <c r="I602"/>
     </row>
     <row r="603" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A603" s="5" t="s">
-        <v>636</v>
-      </c>
-      <c r="C603" s="2">
-        <v>3500</v>
-      </c>
+      <c r="A603" s="12" t="s">
+        <v>412</v>
+      </c>
+      <c r="C603" s="2"/>
       <c r="I603"/>
     </row>
     <row r="604" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A604" s="5" t="s">
-        <v>637</v>
-      </c>
-      <c r="C604" s="2">
-        <v>3500</v>
-      </c>
+      <c r="A604" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="C604" s="2"/>
       <c r="I604"/>
     </row>
     <row r="605" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A605" s="5" t="s">
-        <v>638</v>
-      </c>
-      <c r="C605" s="2">
-        <v>3500</v>
-      </c>
+      <c r="A605" s="12" t="s">
+        <v>414</v>
+      </c>
+      <c r="C605" s="2"/>
       <c r="I605"/>
     </row>
     <row r="606" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A606" s="5" t="s">
-        <v>639</v>
-      </c>
-      <c r="C606" s="2">
-        <v>3500</v>
-      </c>
+      <c r="A606" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="C606" s="2"/>
       <c r="I606"/>
     </row>
     <row r="607" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A607" s="5" t="s">
-        <v>640</v>
-      </c>
-      <c r="C607" s="2">
-        <v>3500</v>
-      </c>
+      <c r="A607" s="12" t="s">
+        <v>416</v>
+      </c>
+      <c r="C607" s="2"/>
       <c r="I607"/>
     </row>
     <row r="608" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A608" s="5" t="s">
-        <v>641</v>
-      </c>
-      <c r="C608" s="2">
-        <v>3500</v>
-      </c>
+      <c r="A608" s="12" t="s">
+        <v>417</v>
+      </c>
+      <c r="C608" s="2"/>
       <c r="I608"/>
     </row>
     <row r="609" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A609" s="5" t="s">
-        <v>642</v>
-      </c>
-      <c r="C609" s="2">
-        <v>3500</v>
-      </c>
+      <c r="A609" s="12" t="s">
+        <v>418</v>
+      </c>
+      <c r="C609" s="2"/>
       <c r="I609"/>
     </row>
     <row r="610" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A610" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="C610" s="2">
-        <v>3500</v>
-      </c>
+      <c r="A610" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="C610" s="2"/>
       <c r="I610"/>
     </row>
     <row r="611" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A611" s="5" t="s">
-        <v>644</v>
-      </c>
-      <c r="B611" s="4"/>
-      <c r="C611" s="2">
-        <v>2200</v>
-      </c>
+      <c r="A611" s="12" t="s">
+        <v>420</v>
+      </c>
+      <c r="C611" s="2"/>
       <c r="I611"/>
     </row>
     <row r="612" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A612" s="5" t="s">
-        <v>645</v>
-      </c>
-      <c r="B612" s="4"/>
-      <c r="C612" s="2">
-        <v>2200</v>
-      </c>
+      <c r="A612" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="C612" s="2"/>
       <c r="I612"/>
     </row>
     <row r="613" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A613" s="5" t="s">
-        <v>646</v>
-      </c>
-      <c r="B613" s="4"/>
-      <c r="C613" s="2">
-        <v>2200</v>
-      </c>
+      <c r="A613" s="12" t="s">
+        <v>422</v>
+      </c>
+      <c r="C613" s="2"/>
       <c r="I613"/>
     </row>
     <row r="614" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A614" s="5" t="s">
-        <v>647</v>
-      </c>
-      <c r="B614" s="4"/>
-      <c r="C614" s="2">
-        <v>2200</v>
-      </c>
+      <c r="A614" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="C614" s="2"/>
       <c r="I614"/>
     </row>
     <row r="615" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A615" s="5" t="s">
-        <v>648</v>
-      </c>
-      <c r="B615" s="4"/>
-      <c r="C615" s="2">
-        <v>2200</v>
-      </c>
+      <c r="A615" s="12" t="s">
+        <v>424</v>
+      </c>
+      <c r="C615" s="2"/>
       <c r="I615"/>
     </row>
     <row r="616" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A616" s="5" t="s">
-        <v>649</v>
-      </c>
-      <c r="B616" s="4"/>
-      <c r="C616" s="2">
-        <v>2200</v>
-      </c>
+      <c r="A616" s="12" t="s">
+        <v>425</v>
+      </c>
+      <c r="C616" s="2"/>
       <c r="I616"/>
     </row>
     <row r="617" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A617" s="5" t="s">
-        <v>650</v>
-      </c>
-      <c r="B617" s="4"/>
-      <c r="C617" s="2">
-        <v>2200</v>
-      </c>
+      <c r="A617" s="12" t="s">
+        <v>426</v>
+      </c>
+      <c r="C617" s="2"/>
       <c r="I617"/>
     </row>
     <row r="618" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A618" s="5" t="s">
-        <v>651</v>
-      </c>
-      <c r="B618" s="4"/>
-      <c r="C618" s="2">
-        <v>2200</v>
-      </c>
+      <c r="A618" s="12" t="s">
+        <v>427</v>
+      </c>
+      <c r="C618" s="2"/>
       <c r="I618"/>
     </row>
     <row r="619" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A619" s="5" t="s">
-        <v>652</v>
-      </c>
-      <c r="B619" s="4"/>
-      <c r="C619" s="2">
-        <v>2200</v>
-      </c>
+      <c r="A619" s="12" t="s">
+        <v>428</v>
+      </c>
+      <c r="C619" s="2"/>
       <c r="I619"/>
     </row>
     <row r="620" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A620" s="5" t="s">
-        <v>653</v>
-      </c>
-      <c r="B620" s="4"/>
-      <c r="C620" s="2">
-        <v>2200</v>
-      </c>
+      <c r="A620" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="C620" s="2"/>
       <c r="I620"/>
     </row>
     <row r="621" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A621" s="5" t="s">
-        <v>654</v>
-      </c>
-      <c r="B621" s="4"/>
-      <c r="C621" s="2">
-        <v>2200</v>
-      </c>
+      <c r="A621" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="C621" s="2"/>
       <c r="I621"/>
     </row>
     <row r="622" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A622" s="5" t="s">
-        <v>655</v>
-      </c>
-      <c r="B622" s="4"/>
-      <c r="C622" s="2">
-        <v>2200</v>
-      </c>
+      <c r="A622" s="12" t="s">
+        <v>431</v>
+      </c>
+      <c r="C622" s="2"/>
       <c r="I622"/>
     </row>
     <row r="623" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A623" s="7"/>
+      <c r="A623" s="12" t="s">
+        <v>432</v>
+      </c>
       <c r="C623" s="2"/>
       <c r="I623"/>
     </row>
     <row r="624" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A624" s="7"/>
+      <c r="A624" s="12" t="s">
+        <v>433</v>
+      </c>
       <c r="C624" s="2"/>
       <c r="I624"/>
     </row>
     <row r="625" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A625" s="7"/>
+      <c r="A625" s="12" t="s">
+        <v>434</v>
+      </c>
       <c r="C625" s="2"/>
       <c r="I625"/>
     </row>
     <row r="626" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A626" s="7"/>
+      <c r="A626" s="12" t="s">
+        <v>435</v>
+      </c>
       <c r="C626" s="2"/>
       <c r="I626"/>
     </row>
     <row r="627" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A627" s="5"/>
+      <c r="A627" s="12" t="s">
+        <v>436</v>
+      </c>
       <c r="C627" s="2"/>
       <c r="I627"/>
     </row>
     <row r="628" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A628" s="5"/>
+      <c r="A628" s="12" t="s">
+        <v>437</v>
+      </c>
       <c r="C628" s="2"/>
       <c r="I628"/>
     </row>
     <row r="629" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A629" s="5"/>
+      <c r="A629" s="12" t="s">
+        <v>438</v>
+      </c>
       <c r="C629" s="2"/>
       <c r="I629"/>
     </row>
     <row r="630" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A630" s="5"/>
+      <c r="A630" s="12" t="s">
+        <v>439</v>
+      </c>
       <c r="C630" s="2"/>
       <c r="I630"/>
     </row>
     <row r="631" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A631" s="5"/>
+      <c r="A631" s="12" t="s">
+        <v>440</v>
+      </c>
       <c r="C631" s="2"/>
       <c r="I631"/>
     </row>
     <row r="632" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A632" s="5"/>
+      <c r="A632" s="12" t="s">
+        <v>441</v>
+      </c>
       <c r="C632" s="2"/>
       <c r="I632"/>
     </row>
     <row r="633" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A633" s="5"/>
+      <c r="A633" s="12" t="s">
+        <v>442</v>
+      </c>
       <c r="C633" s="2"/>
       <c r="I633"/>
     </row>
     <row r="634" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A634" s="5"/>
+      <c r="A634" s="12" t="s">
+        <v>443</v>
+      </c>
       <c r="C634" s="2"/>
       <c r="I634"/>
     </row>
     <row r="635" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A635" s="5"/>
+      <c r="A635" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="C635" s="2">
+        <v>3500</v>
+      </c>
       <c r="I635"/>
     </row>
     <row r="636" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A636" s="5"/>
+      <c r="A636" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="C636" s="2">
+        <v>3500</v>
+      </c>
       <c r="I636"/>
     </row>
     <row r="637" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A637" s="5"/>
-      <c r="C637" s="2"/>
+      <c r="A637" s="5" t="s">
+        <v>634</v>
+      </c>
+      <c r="C637" s="2">
+        <v>3500</v>
+      </c>
       <c r="I637"/>
     </row>
     <row r="638" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A638" s="5"/>
+      <c r="A638" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="C638" s="2">
+        <v>3500</v>
+      </c>
       <c r="I638"/>
     </row>
     <row r="639" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A639" s="5"/>
+      <c r="A639" s="5" t="s">
+        <v>636</v>
+      </c>
+      <c r="C639" s="2">
+        <v>3500</v>
+      </c>
       <c r="I639"/>
     </row>
     <row r="640" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A640" s="5"/>
-      <c r="C640" s="2"/>
+      <c r="A640" s="5" t="s">
+        <v>637</v>
+      </c>
+      <c r="C640" s="2">
+        <v>3500</v>
+      </c>
       <c r="I640"/>
     </row>
     <row r="641" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A641" s="5"/>
+      <c r="A641" s="5" t="s">
+        <v>638</v>
+      </c>
+      <c r="C641" s="2">
+        <v>3500</v>
+      </c>
       <c r="I641"/>
     </row>
     <row r="642" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A642" s="5"/>
+      <c r="A642" s="5" t="s">
+        <v>639</v>
+      </c>
+      <c r="C642" s="2">
+        <v>3500</v>
+      </c>
       <c r="I642"/>
     </row>
     <row r="643" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A643" s="5"/>
-      <c r="C643" s="2"/>
+      <c r="A643" s="5" t="s">
+        <v>640</v>
+      </c>
+      <c r="C643" s="2">
+        <v>3500</v>
+      </c>
       <c r="I643"/>
     </row>
     <row r="644" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A644" s="5"/>
+      <c r="A644" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="C644" s="2">
+        <v>3500</v>
+      </c>
       <c r="I644"/>
     </row>
     <row r="645" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A645" s="5"/>
+      <c r="A645" s="5" t="s">
+        <v>642</v>
+      </c>
+      <c r="C645" s="2">
+        <v>3500</v>
+      </c>
       <c r="I645"/>
     </row>
     <row r="646" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A646" s="5"/>
-      <c r="C646" s="2"/>
+      <c r="A646" s="5" t="s">
+        <v>643</v>
+      </c>
+      <c r="C646" s="2">
+        <v>3500</v>
+      </c>
       <c r="I646"/>
     </row>
     <row r="647" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A647" s="5"/>
+      <c r="A647" s="5" t="s">
+        <v>644</v>
+      </c>
+      <c r="B647" s="4"/>
+      <c r="C647" s="2">
+        <v>2200</v>
+      </c>
       <c r="I647"/>
     </row>
     <row r="648" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A648" s="5"/>
+      <c r="A648" s="5" t="s">
+        <v>645</v>
+      </c>
+      <c r="B648" s="4"/>
+      <c r="C648" s="2">
+        <v>2200</v>
+      </c>
       <c r="I648"/>
     </row>
     <row r="649" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A649" s="5"/>
-      <c r="C649" s="2"/>
+      <c r="A649" s="5" t="s">
+        <v>646</v>
+      </c>
+      <c r="B649" s="4"/>
+      <c r="C649" s="2">
+        <v>2200</v>
+      </c>
       <c r="I649"/>
     </row>
     <row r="650" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A650" s="5"/>
+      <c r="A650" s="5" t="s">
+        <v>647</v>
+      </c>
+      <c r="B650" s="4"/>
+      <c r="C650" s="2">
+        <v>2200</v>
+      </c>
       <c r="I650"/>
     </row>
     <row r="651" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A651" s="5"/>
+      <c r="A651" s="5" t="s">
+        <v>648</v>
+      </c>
+      <c r="B651" s="4"/>
+      <c r="C651" s="2">
+        <v>2200</v>
+      </c>
       <c r="I651"/>
     </row>
     <row r="652" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A652" s="5"/>
-      <c r="C652" s="2"/>
+      <c r="A652" s="5" t="s">
+        <v>649</v>
+      </c>
+      <c r="B652" s="4"/>
+      <c r="C652" s="2">
+        <v>2200</v>
+      </c>
       <c r="I652"/>
     </row>
     <row r="653" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A653" s="5"/>
+      <c r="A653" s="5" t="s">
+        <v>650</v>
+      </c>
+      <c r="B653" s="4"/>
+      <c r="C653" s="2">
+        <v>2200</v>
+      </c>
       <c r="I653"/>
     </row>
     <row r="654" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A654" s="5"/>
+      <c r="A654" s="5" t="s">
+        <v>651</v>
+      </c>
+      <c r="B654" s="4"/>
+      <c r="C654" s="2">
+        <v>2200</v>
+      </c>
       <c r="I654"/>
     </row>
     <row r="655" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A655" s="5"/>
-      <c r="C655" s="2"/>
+      <c r="A655" s="5" t="s">
+        <v>652</v>
+      </c>
+      <c r="B655" s="4"/>
+      <c r="C655" s="2">
+        <v>2200</v>
+      </c>
       <c r="I655"/>
     </row>
     <row r="656" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A656" s="5"/>
+      <c r="A656" s="5" t="s">
+        <v>653</v>
+      </c>
+      <c r="B656" s="4"/>
+      <c r="C656" s="2">
+        <v>2200</v>
+      </c>
       <c r="I656"/>
     </row>
     <row r="657" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A657" s="5"/>
+      <c r="A657" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="B657" s="4"/>
+      <c r="C657" s="2">
+        <v>2200</v>
+      </c>
       <c r="I657"/>
     </row>
     <row r="658" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A658" s="5"/>
-      <c r="C658" s="2"/>
+      <c r="A658" s="5" t="s">
+        <v>655</v>
+      </c>
+      <c r="B658" s="4"/>
+      <c r="C658" s="2">
+        <v>2200</v>
+      </c>
       <c r="I658"/>
     </row>
     <row r="659" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A659" s="5"/>
+      <c r="A659" s="5" t="s">
+        <v>693</v>
+      </c>
+      <c r="B659" s="4"/>
+      <c r="C659" s="2">
+        <v>3000</v>
+      </c>
       <c r="I659"/>
     </row>
     <row r="660" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A660" s="5"/>
+      <c r="A660" s="5" t="s">
+        <v>694</v>
+      </c>
+      <c r="B660" s="4"/>
+      <c r="C660" s="2">
+        <v>3000</v>
+      </c>
       <c r="I660"/>
     </row>
     <row r="661" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A661" s="5"/>
-      <c r="C661" s="2"/>
+      <c r="A661" s="5" t="s">
+        <v>695</v>
+      </c>
+      <c r="B661" s="4"/>
+      <c r="C661" s="2">
+        <v>3000</v>
+      </c>
       <c r="I661"/>
     </row>
     <row r="662" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A662" s="5"/>
+      <c r="A662" s="5" t="s">
+        <v>696</v>
+      </c>
+      <c r="B662" s="4"/>
+      <c r="C662" s="2">
+        <v>3000</v>
+      </c>
       <c r="I662"/>
     </row>
     <row r="663" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A663" s="5"/>
+      <c r="A663" s="5" t="s">
+        <v>697</v>
+      </c>
+      <c r="B663" s="4"/>
+      <c r="C663" s="2">
+        <v>3000</v>
+      </c>
       <c r="I663"/>
     </row>
     <row r="664" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A664" s="5"/>
-      <c r="C664" s="2"/>
+      <c r="A664" s="5" t="s">
+        <v>698</v>
+      </c>
+      <c r="B664" s="4"/>
+      <c r="C664" s="2">
+        <v>3000</v>
+      </c>
       <c r="I664"/>
     </row>
     <row r="665" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A665" s="5"/>
+      <c r="A665" s="5" t="s">
+        <v>699</v>
+      </c>
+      <c r="B665" s="4"/>
+      <c r="C665" s="2">
+        <v>3000</v>
+      </c>
       <c r="I665"/>
     </row>
     <row r="666" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A666" s="5"/>
+      <c r="A666" s="5" t="s">
+        <v>700</v>
+      </c>
+      <c r="B666" s="4"/>
+      <c r="C666" s="2">
+        <v>3000</v>
+      </c>
       <c r="I666"/>
     </row>
     <row r="667" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A667" s="5"/>
-      <c r="C667" s="2"/>
+      <c r="A667" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="B667" s="4"/>
+      <c r="C667" s="2">
+        <v>3000</v>
+      </c>
       <c r="I667"/>
     </row>
     <row r="668" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A668" s="5"/>
+      <c r="A668" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="B668" s="4"/>
+      <c r="C668" s="2">
+        <v>3000</v>
+      </c>
       <c r="I668"/>
     </row>
     <row r="669" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A669" s="5"/>
+      <c r="A669" s="5" t="s">
+        <v>703</v>
+      </c>
+      <c r="B669" s="4"/>
+      <c r="C669" s="2">
+        <v>3000</v>
+      </c>
       <c r="I669"/>
     </row>
     <row r="670" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A670" s="5"/>
-      <c r="C670" s="2"/>
-      <c r="I670"/>
+      <c r="A670" s="5" t="s">
+        <v>704</v>
+      </c>
+      <c r="B670" s="4"/>
+      <c r="C670" s="2">
+        <v>3000</v>
+      </c>
     </row>
     <row r="671" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A671" s="5"/>
@@ -9225,148 +9699,160 @@
     <row r="672" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A672" s="5"/>
     </row>
-    <row r="673" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A673" s="5"/>
-    </row>
-    <row r="674" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C673" s="2"/>
+    </row>
+    <row r="674" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A674" s="5"/>
     </row>
-    <row r="675" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A675" s="5"/>
     </row>
-    <row r="676" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A676" s="5"/>
-    </row>
-    <row r="677" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C676" s="2"/>
+    </row>
+    <row r="677" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A677" s="5"/>
     </row>
-    <row r="678" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A678" s="5"/>
     </row>
-    <row r="679" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A679" s="5"/>
-    </row>
-    <row r="680" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C679" s="2"/>
+    </row>
+    <row r="680" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A680" s="5"/>
     </row>
-    <row r="681" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A681" s="5"/>
     </row>
-    <row r="682" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A682" s="5"/>
-    </row>
-    <row r="683" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C682" s="2"/>
+    </row>
+    <row r="683" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A683" s="5"/>
     </row>
-    <row r="684" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A684" s="5"/>
     </row>
-    <row r="685" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A685" s="5"/>
-    </row>
-    <row r="686" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C685" s="2"/>
+    </row>
+    <row r="686" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A686" s="5"/>
     </row>
-    <row r="687" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A687" s="5"/>
     </row>
-    <row r="688" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A688" s="5"/>
-    </row>
-    <row r="689" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C688" s="2"/>
+    </row>
+    <row r="689" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A689" s="5"/>
     </row>
-    <row r="690" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A690" s="5"/>
     </row>
-    <row r="691" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A691" s="5"/>
-    </row>
-    <row r="692" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C691" s="2"/>
+    </row>
+    <row r="692" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A692" s="5"/>
     </row>
-    <row r="693" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A693" s="5"/>
     </row>
-    <row r="694" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A694" s="5"/>
-    </row>
-    <row r="695" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C694" s="2"/>
+    </row>
+    <row r="695" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A695" s="5"/>
     </row>
-    <row r="696" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A696" s="5"/>
     </row>
-    <row r="697" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A697" s="5"/>
-    </row>
-    <row r="698" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C697" s="2"/>
+    </row>
+    <row r="698" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A698" s="5"/>
     </row>
-    <row r="699" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A699" s="5"/>
     </row>
-    <row r="700" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A700" s="5"/>
-    </row>
-    <row r="701" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C700" s="2"/>
+    </row>
+    <row r="701" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A701" s="5"/>
     </row>
-    <row r="702" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A702" s="5"/>
     </row>
-    <row r="703" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A703" s="5"/>
-    </row>
-    <row r="704" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C703" s="2"/>
+    </row>
+    <row r="704" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A704" s="5"/>
     </row>
-    <row r="705" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A705" s="5"/>
     </row>
-    <row r="706" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A706" s="5"/>
-    </row>
-    <row r="707" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C706" s="2"/>
+    </row>
+    <row r="707" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A707" s="5"/>
     </row>
-    <row r="708" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A708" s="5"/>
     </row>
-    <row r="709" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A709" s="5"/>
     </row>
-    <row r="710" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A710" s="5"/>
     </row>
-    <row r="711" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A711" s="5"/>
     </row>
-    <row r="712" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A712" s="5"/>
     </row>
-    <row r="713" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A713" s="5"/>
     </row>
-    <row r="714" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A714" s="5"/>
     </row>
-    <row r="715" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A715" s="5"/>
     </row>
-    <row r="716" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A716" s="5"/>
     </row>
-    <row r="717" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A717" s="5"/>
     </row>
-    <row r="718" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A718" s="5"/>
     </row>
-    <row r="719" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A719" s="5"/>
     </row>
-    <row r="720" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A720" s="5"/>
     </row>
     <row r="721" spans="1:1" x14ac:dyDescent="0.25">
@@ -9519,10 +10005,118 @@
     <row r="770" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A770" s="5"/>
     </row>
+    <row r="771" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A771" s="5"/>
+    </row>
+    <row r="772" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A772" s="5"/>
+    </row>
+    <row r="773" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A773" s="5"/>
+    </row>
+    <row r="774" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A774" s="5"/>
+    </row>
+    <row r="775" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A775" s="5"/>
+    </row>
+    <row r="776" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A776" s="5"/>
+    </row>
+    <row r="777" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A777" s="5"/>
+    </row>
+    <row r="778" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A778" s="5"/>
+    </row>
+    <row r="779" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A779" s="5"/>
+    </row>
+    <row r="780" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A780" s="5"/>
+    </row>
+    <row r="781" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A781" s="5"/>
+    </row>
+    <row r="782" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A782" s="5"/>
+    </row>
+    <row r="783" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A783" s="5"/>
+    </row>
+    <row r="784" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A784" s="5"/>
+    </row>
+    <row r="785" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A785" s="5"/>
+    </row>
+    <row r="786" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A786" s="5"/>
+    </row>
+    <row r="787" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A787" s="5"/>
+    </row>
+    <row r="788" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A788" s="5"/>
+    </row>
+    <row r="789" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A789" s="5"/>
+    </row>
+    <row r="790" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A790" s="5"/>
+    </row>
+    <row r="791" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A791" s="5"/>
+    </row>
+    <row r="792" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A792" s="5"/>
+    </row>
+    <row r="793" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A793" s="5"/>
+    </row>
+    <row r="794" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A794" s="5"/>
+    </row>
+    <row r="795" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A795" s="5"/>
+    </row>
+    <row r="796" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A796" s="5"/>
+    </row>
+    <row r="797" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A797" s="5"/>
+    </row>
+    <row r="798" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A798" s="5"/>
+    </row>
+    <row r="799" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A799" s="5"/>
+    </row>
+    <row r="800" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A800" s="5"/>
+    </row>
+    <row r="801" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A801" s="5"/>
+    </row>
+    <row r="802" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A802" s="5"/>
+    </row>
+    <row r="803" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A803" s="5"/>
+    </row>
+    <row r="804" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A804" s="5"/>
+    </row>
+    <row r="805" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A805" s="5"/>
+    </row>
+    <row r="806" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A806" s="5"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B626" xr:uid="{1FD8F914-C444-47BA-9F60-B10F23023A52}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B634">
-      <sortCondition ref="A1:A626"/>
+  <autoFilter ref="A1:B662" xr:uid="{1FD8F914-C444-47BA-9F60-B10F23023A52}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B670">
+      <sortCondition ref="A1:A662"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9539,16 +10133,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>588</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>589</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>612</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="10" t="s">
         <v>613</v>
       </c>
     </row>
@@ -9556,7 +10150,7 @@
       <c r="A2" t="s">
         <v>590</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="7">
         <v>900</v>
       </c>
       <c r="E2" t="s">
@@ -9570,7 +10164,7 @@
       <c r="A3" t="s">
         <v>591</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="7">
         <v>1000</v>
       </c>
       <c r="E3" t="s">
@@ -9738,8 +10332,12 @@
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
+      <c r="A24" t="s">
+        <v>692</v>
+      </c>
+      <c r="B24">
+        <v>100</v>
+      </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
